--- a/src/main/resources/sql/20260819/app层/数据字典.xlsx
+++ b/src/main/resources/sql/20260819/app层/数据字典.xlsx
@@ -1204,7 +1204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M596"/>
+  <dimension ref="A1:M595"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="30.9909090909091" customWidth="1" style="25" min="1" max="1"/>
@@ -13405,66 +13405,80 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
+      <c r="A340" s="22" t="inlineStr">
         <is>
           <t>app_guarantor_info</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B340" s="22" t="inlineStr">
         <is>
           <t>担保人信息表</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>creditSum</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>DECIMAL(18,2)</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>授信金额（万元，2026-09-03 新增）</t>
-        </is>
-      </c>
+      <c r="C340" s="22" t="inlineStr">
+        <is>
+          <t>inputtime</t>
+        </is>
+      </c>
+      <c r="D340" s="22" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E340" s="22" t="inlineStr"/>
+      <c r="F340" s="22" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G340" s="22" t="inlineStr">
+        <is>
+          <t>入库时间</t>
+        </is>
+      </c>
+      <c r="H340" s="22" t="inlineStr"/>
+      <c r="I340" s="22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J340" s="8" t="n"/>
+      <c r="K340" s="8" t="n"/>
     </row>
     <row r="341">
-      <c r="A341" s="22" t="inlineStr">
-        <is>
-          <t>app_guarantor_info</t>
-        </is>
-      </c>
-      <c r="B341" s="22" t="inlineStr">
-        <is>
-          <t>担保人信息表</t>
-        </is>
-      </c>
-      <c r="C341" s="22" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D341" s="22" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E341" s="22" t="inlineStr"/>
-      <c r="F341" s="22" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G341" s="22" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H341" s="22" t="inlineStr"/>
-      <c r="I341" s="22" t="inlineStr">
+      <c r="A341" s="4" t="inlineStr">
+        <is>
+          <t>app_guarantor_credit_info</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>担保人征信表</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E341" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F341" s="4" t="inlineStr"/>
+      <c r="G341" s="4" t="inlineStr"/>
+      <c r="H341" s="4" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I341" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -13473,44 +13487,52 @@
       <c r="K341" s="8" t="n"/>
     </row>
     <row r="342">
-      <c r="A342" s="4" t="inlineStr">
+      <c r="A342" s="6" t="inlineStr">
         <is>
           <t>app_guarantor_credit_info</t>
         </is>
       </c>
-      <c r="B342" s="4" t="inlineStr">
+      <c r="B342" s="6" t="inlineStr">
         <is>
           <t>担保人征信表</t>
         </is>
       </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D342" s="4" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E342" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F342" s="4" t="inlineStr"/>
-      <c r="G342" s="4" t="inlineStr"/>
-      <c r="H342" s="4" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I342" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J342" s="8" t="n"/>
+      <c r="C342" s="6" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E342" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F342" s="6" t="inlineStr"/>
+      <c r="G342" s="6" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I342" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J342" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K342" s="8" t="n"/>
     </row>
     <row r="343">
@@ -13526,7 +13548,7 @@
       </c>
       <c r="C343" s="6" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D343" s="6" t="inlineStr">
@@ -13534,15 +13556,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E343" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E343" s="6" t="inlineStr"/>
       <c r="F343" s="6" t="inlineStr"/>
       <c r="G343" s="6" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H343" s="6" t="inlineStr">
@@ -13575,174 +13593,162 @@
       </c>
       <c r="C344" s="6" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D344" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E344" s="6" t="inlineStr"/>
       <c r="F344" s="6" t="inlineStr"/>
       <c r="G344" s="6" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H344" s="6" t="inlineStr">
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H344" s="6" t="inlineStr"/>
+      <c r="I344" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J344" s="8" t="n"/>
+      <c r="K344" s="8" t="n"/>
+    </row>
+    <row r="345" ht="28" customHeight="1" s="25">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>app_guarantor_credit_info</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>担保人征信表</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>guarantorId</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>担保人客户编号</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="6" t="inlineStr">
+        <is>
+          <t>app_guarantor_credit_info</t>
+        </is>
+      </c>
+      <c r="B346" s="6" t="inlineStr">
+        <is>
+          <t>担保人征信表</t>
+        </is>
+      </c>
+      <c r="C346" s="6" t="inlineStr">
+        <is>
+          <t>guarantorName</t>
+        </is>
+      </c>
+      <c r="D346" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(128)</t>
+        </is>
+      </c>
+      <c r="E346" s="6" t="inlineStr"/>
+      <c r="F346" s="6" t="inlineStr"/>
+      <c r="G346" s="6" t="inlineStr">
+        <is>
+          <t>担保人</t>
+        </is>
+      </c>
+      <c r="H346" s="6" t="inlineStr">
         <is>
           <t>IDX</t>
         </is>
       </c>
-      <c r="I344" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J344" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K344" s="8" t="n"/>
-    </row>
-    <row r="345" ht="28" customHeight="1" s="25">
-      <c r="A345" s="6" t="inlineStr">
+      <c r="I346" s="6" t="inlineStr"/>
+      <c r="J346" s="8" t="n"/>
+      <c r="K346" s="8" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="17" t="inlineStr">
         <is>
           <t>app_guarantor_credit_info</t>
         </is>
       </c>
-      <c r="B345" s="6" t="inlineStr">
+      <c r="B347" s="17" t="inlineStr">
         <is>
           <t>担保人征信表</t>
         </is>
       </c>
-      <c r="C345" s="6" t="inlineStr">
-        <is>
-          <t>customerName</t>
-        </is>
-      </c>
-      <c r="D345" s="6" t="inlineStr">
+      <c r="C347" s="17" t="inlineStr">
+        <is>
+          <t>zxReportNo</t>
+        </is>
+      </c>
+      <c r="D347" s="17" t="inlineStr">
         <is>
           <t>VARCHAR(128)</t>
         </is>
       </c>
-      <c r="E345" s="6" t="inlineStr"/>
-      <c r="F345" s="6" t="inlineStr"/>
-      <c r="G345" s="6" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="H345" s="6" t="inlineStr"/>
-      <c r="I345" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J345" s="8" t="n"/>
-      <c r="K345" s="8" t="n"/>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
+      <c r="E347" s="17" t="n"/>
+      <c r="F347" s="17" t="n"/>
+      <c r="G347" s="17" t="inlineStr">
+        <is>
+          <t>征信报告记录号</t>
+        </is>
+      </c>
+      <c r="H347" s="17" t="n"/>
+      <c r="I347" s="17" t="n"/>
+      <c r="J347" s="24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K347" s="8" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="6" t="inlineStr">
         <is>
           <t>app_guarantor_credit_info</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B348" s="6" t="inlineStr">
         <is>
           <t>担保人征信表</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>guarantorId</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>VARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>担保人客户编号</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="6" t="inlineStr">
-        <is>
-          <t>app_guarantor_credit_info</t>
-        </is>
-      </c>
-      <c r="B347" s="6" t="inlineStr">
-        <is>
-          <t>担保人征信表</t>
-        </is>
-      </c>
-      <c r="C347" s="6" t="inlineStr">
-        <is>
-          <t>guarantorName</t>
-        </is>
-      </c>
-      <c r="D347" s="6" t="inlineStr">
-        <is>
-          <t>VARCHAR(128)</t>
-        </is>
-      </c>
-      <c r="E347" s="6" t="inlineStr"/>
-      <c r="F347" s="6" t="inlineStr"/>
-      <c r="G347" s="6" t="inlineStr">
-        <is>
-          <t>担保人</t>
-        </is>
-      </c>
-      <c r="H347" s="6" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
-      <c r="I347" s="6" t="inlineStr"/>
-      <c r="J347" s="8" t="n"/>
-      <c r="K347" s="8" t="n"/>
-    </row>
-    <row r="348">
-      <c r="A348" s="17" t="inlineStr">
-        <is>
-          <t>app_guarantor_credit_info</t>
-        </is>
-      </c>
-      <c r="B348" s="17" t="inlineStr">
-        <is>
-          <t>担保人征信表</t>
-        </is>
-      </c>
-      <c r="C348" s="17" t="inlineStr">
-        <is>
-          <t>zxReportNo</t>
-        </is>
-      </c>
-      <c r="D348" s="17" t="inlineStr">
-        <is>
-          <t>VARCHAR(128)</t>
-        </is>
-      </c>
-      <c r="E348" s="17" t="n"/>
-      <c r="F348" s="17" t="n"/>
-      <c r="G348" s="17" t="inlineStr">
-        <is>
-          <t>征信报告记录号</t>
-        </is>
-      </c>
-      <c r="H348" s="17" t="n"/>
-      <c r="I348" s="17" t="n"/>
-      <c r="J348" s="24" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="C348" s="6" t="inlineStr">
+        <is>
+          <t>queryTime</t>
+        </is>
+      </c>
+      <c r="D348" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(32)</t>
+        </is>
+      </c>
+      <c r="E348" s="6" t="inlineStr"/>
+      <c r="F348" s="6" t="inlineStr"/>
+      <c r="G348" s="6" t="inlineStr">
+        <is>
+          <t>征信查询时间</t>
+        </is>
+      </c>
+      <c r="H348" s="6" t="inlineStr"/>
+      <c r="I348" s="6" t="inlineStr"/>
+      <c r="J348" s="8" t="n"/>
       <c r="K348" s="8" t="n"/>
     </row>
     <row r="349">
@@ -13758,19 +13764,19 @@
       </c>
       <c r="C349" s="6" t="inlineStr">
         <is>
-          <t>queryTime</t>
+          <t>totalLoanBal</t>
         </is>
       </c>
       <c r="D349" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="E349" s="6" t="inlineStr"/>
       <c r="F349" s="6" t="inlineStr"/>
       <c r="G349" s="6" t="inlineStr">
         <is>
-          <t>征信查询时间</t>
+          <t>贷款余额合计（万元）</t>
         </is>
       </c>
       <c r="H349" s="6" t="inlineStr"/>
@@ -13791,7 +13797,7 @@
       </c>
       <c r="C350" s="6" t="inlineStr">
         <is>
-          <t>totalLoanBal</t>
+          <t>operateLoanBal</t>
         </is>
       </c>
       <c r="D350" s="6" t="inlineStr">
@@ -13803,7 +13809,7 @@
       <c r="F350" s="6" t="inlineStr"/>
       <c r="G350" s="6" t="inlineStr">
         <is>
-          <t>贷款余额合计（万元）</t>
+          <t>经营性贷款余额合计（万元）</t>
         </is>
       </c>
       <c r="H350" s="6" t="inlineStr"/>
@@ -13824,7 +13830,7 @@
       </c>
       <c r="C351" s="6" t="inlineStr">
         <is>
-          <t>operateLoanBal</t>
+          <t>consumeLoanBal</t>
         </is>
       </c>
       <c r="D351" s="6" t="inlineStr">
@@ -13836,7 +13842,7 @@
       <c r="F351" s="6" t="inlineStr"/>
       <c r="G351" s="6" t="inlineStr">
         <is>
-          <t>经营性贷款余额合计（万元）</t>
+          <t>消费类贷款余额合计（万元）</t>
         </is>
       </c>
       <c r="H351" s="6" t="inlineStr"/>
@@ -13857,7 +13863,7 @@
       </c>
       <c r="C352" s="6" t="inlineStr">
         <is>
-          <t>consumeLoanBal</t>
+          <t>houseLoanBal</t>
         </is>
       </c>
       <c r="D352" s="6" t="inlineStr">
@@ -13869,7 +13875,7 @@
       <c r="F352" s="6" t="inlineStr"/>
       <c r="G352" s="6" t="inlineStr">
         <is>
-          <t>消费类贷款余额合计（万元）</t>
+          <t>住房类贷款余额合计（万元）</t>
         </is>
       </c>
       <c r="H352" s="6" t="inlineStr"/>
@@ -13890,7 +13896,7 @@
       </c>
       <c r="C353" s="6" t="inlineStr">
         <is>
-          <t>houseLoanBal</t>
+          <t>otherLoanBal</t>
         </is>
       </c>
       <c r="D353" s="6" t="inlineStr">
@@ -13902,7 +13908,7 @@
       <c r="F353" s="6" t="inlineStr"/>
       <c r="G353" s="6" t="inlineStr">
         <is>
-          <t>住房类贷款余额合计（万元）</t>
+          <t>其他贷款余额合计（万元）</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr"/>
@@ -13923,19 +13929,19 @@
       </c>
       <c r="C354" s="6" t="inlineStr">
         <is>
-          <t>otherLoanBal</t>
+          <t>totalLoanCount</t>
         </is>
       </c>
       <c r="D354" s="6" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E354" s="6" t="inlineStr"/>
       <c r="F354" s="6" t="inlineStr"/>
       <c r="G354" s="6" t="inlineStr">
         <is>
-          <t>其他贷款余额合计（万元）</t>
+          <t>贷款机构数</t>
         </is>
       </c>
       <c r="H354" s="6" t="inlineStr"/>
@@ -13956,7 +13962,7 @@
       </c>
       <c r="C355" s="6" t="inlineStr">
         <is>
-          <t>totalLoanCount</t>
+          <t>operateLoanCount</t>
         </is>
       </c>
       <c r="D355" s="6" t="inlineStr">
@@ -13968,7 +13974,7 @@
       <c r="F355" s="6" t="inlineStr"/>
       <c r="G355" s="6" t="inlineStr">
         <is>
-          <t>贷款机构数</t>
+          <t>经营性贷款机构数</t>
         </is>
       </c>
       <c r="H355" s="6" t="inlineStr"/>
@@ -13989,7 +13995,7 @@
       </c>
       <c r="C356" s="6" t="inlineStr">
         <is>
-          <t>operateLoanCount</t>
+          <t>consumeLoanCount</t>
         </is>
       </c>
       <c r="D356" s="6" t="inlineStr">
@@ -14001,7 +14007,7 @@
       <c r="F356" s="6" t="inlineStr"/>
       <c r="G356" s="6" t="inlineStr">
         <is>
-          <t>经营性贷款机构数</t>
+          <t>消费类贷款机构数</t>
         </is>
       </c>
       <c r="H356" s="6" t="inlineStr"/>
@@ -14022,7 +14028,7 @@
       </c>
       <c r="C357" s="6" t="inlineStr">
         <is>
-          <t>consumeLoanCount</t>
+          <t>houseLoanCount</t>
         </is>
       </c>
       <c r="D357" s="6" t="inlineStr">
@@ -14034,7 +14040,7 @@
       <c r="F357" s="6" t="inlineStr"/>
       <c r="G357" s="6" t="inlineStr">
         <is>
-          <t>消费类贷款机构数</t>
+          <t>住房类贷款机构数</t>
         </is>
       </c>
       <c r="H357" s="6" t="inlineStr"/>
@@ -14055,7 +14061,7 @@
       </c>
       <c r="C358" s="6" t="inlineStr">
         <is>
-          <t>houseLoanCount</t>
+          <t>otherLoanCount</t>
         </is>
       </c>
       <c r="D358" s="6" t="inlineStr">
@@ -14067,7 +14073,7 @@
       <c r="F358" s="6" t="inlineStr"/>
       <c r="G358" s="6" t="inlineStr">
         <is>
-          <t>住房类贷款机构数</t>
+          <t>其他贷款机构数</t>
         </is>
       </c>
       <c r="H358" s="6" t="inlineStr"/>
@@ -14088,19 +14094,19 @@
       </c>
       <c r="C359" s="6" t="inlineStr">
         <is>
-          <t>otherLoanCount</t>
+          <t>bzcBal</t>
         </is>
       </c>
       <c r="D359" s="6" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="E359" s="6" t="inlineStr"/>
       <c r="F359" s="6" t="inlineStr"/>
       <c r="G359" s="6" t="inlineStr">
         <is>
-          <t>其他贷款机构数</t>
+          <t>被追偿余额（万元）</t>
         </is>
       </c>
       <c r="H359" s="6" t="inlineStr"/>
@@ -14121,7 +14127,7 @@
       </c>
       <c r="C360" s="6" t="inlineStr">
         <is>
-          <t>bzcBal</t>
+          <t>badBal</t>
         </is>
       </c>
       <c r="D360" s="6" t="inlineStr">
@@ -14133,7 +14139,7 @@
       <c r="F360" s="6" t="inlineStr"/>
       <c r="G360" s="6" t="inlineStr">
         <is>
-          <t>被追偿余额（万元）</t>
+          <t>呆账余额（万元）</t>
         </is>
       </c>
       <c r="H360" s="6" t="inlineStr"/>
@@ -14154,7 +14160,7 @@
       </c>
       <c r="C361" s="6" t="inlineStr">
         <is>
-          <t>badBal</t>
+          <t>loanCurrentOverdue</t>
         </is>
       </c>
       <c r="D361" s="6" t="inlineStr">
@@ -14166,7 +14172,7 @@
       <c r="F361" s="6" t="inlineStr"/>
       <c r="G361" s="6" t="inlineStr">
         <is>
-          <t>呆账余额（万元）</t>
+          <t>贷款当前逾期总金额（万元）</t>
         </is>
       </c>
       <c r="H361" s="6" t="inlineStr"/>
@@ -14187,7 +14193,7 @@
       </c>
       <c r="C362" s="6" t="inlineStr">
         <is>
-          <t>loanCurrentOverdue</t>
+          <t>cardCurrentOverdue</t>
         </is>
       </c>
       <c r="D362" s="6" t="inlineStr">
@@ -14199,7 +14205,7 @@
       <c r="F362" s="6" t="inlineStr"/>
       <c r="G362" s="6" t="inlineStr">
         <is>
-          <t>贷款当前逾期总金额（万元）</t>
+          <t>贷记卡当前逾期总金额（万元）</t>
         </is>
       </c>
       <c r="H362" s="6" t="inlineStr"/>
@@ -14220,7 +14226,7 @@
       </c>
       <c r="C363" s="6" t="inlineStr">
         <is>
-          <t>cardCurrentOverdue</t>
+          <t>guaranteeOverdueAmt</t>
         </is>
       </c>
       <c r="D363" s="6" t="inlineStr">
@@ -14232,7 +14238,7 @@
       <c r="F363" s="6" t="inlineStr"/>
       <c r="G363" s="6" t="inlineStr">
         <is>
-          <t>贷记卡当前逾期总金额（万元）</t>
+          <t>对外担保（相关还款责任）当前逾期金额（万元）</t>
         </is>
       </c>
       <c r="H363" s="6" t="inlineStr"/>
@@ -14253,7 +14259,7 @@
       </c>
       <c r="C364" s="6" t="inlineStr">
         <is>
-          <t>guaranteeOverdueAmt</t>
+          <t>nonBankGuaranteeBal</t>
         </is>
       </c>
       <c r="D364" s="6" t="inlineStr">
@@ -14265,7 +14271,7 @@
       <c r="F364" s="6" t="inlineStr"/>
       <c r="G364" s="6" t="inlineStr">
         <is>
-          <t>对外担保（相关还款责任）当前逾期金额（万元）</t>
+          <t>在非银机构对外担保余额（万元，上游直给：qy_fyjg_dwdb_bal/gr_fyjg_dwdb_bal）</t>
         </is>
       </c>
       <c r="H364" s="6" t="inlineStr"/>
@@ -14286,7 +14292,7 @@
       </c>
       <c r="C365" s="6" t="inlineStr">
         <is>
-          <t>nonBankGuaranteeBal</t>
+          <t>nonBankHighRateLoan</t>
         </is>
       </c>
       <c r="D365" s="6" t="inlineStr">
@@ -14298,7 +14304,7 @@
       <c r="F365" s="6" t="inlineStr"/>
       <c r="G365" s="6" t="inlineStr">
         <is>
-          <t>在非银机构对外担保余额（万元，上游直给：qy_fyjg_dwdb_bal/gr_fyjg_dwdb_bal）</t>
+          <t>非银机构较高利率借款推算利率最大值（%，上游直给：qy_fyjg_gjlv_loan_max/gr_fyjg_gjlv_loan_max；较高利率判断依据）</t>
         </is>
       </c>
       <c r="H365" s="6" t="inlineStr"/>
@@ -14319,7 +14325,7 @@
       </c>
       <c r="C366" s="6" t="inlineStr">
         <is>
-          <t>nonBankHighRateLoan</t>
+          <t>guaranteeAbnormalBal</t>
         </is>
       </c>
       <c r="D366" s="6" t="inlineStr">
@@ -14331,7 +14337,7 @@
       <c r="F366" s="6" t="inlineStr"/>
       <c r="G366" s="6" t="inlineStr">
         <is>
-          <t>非银机构较高利率借款推算利率最大值（%，上游直给：qy_fyjg_gjlv_loan_max/gr_fyjg_gjlv_loan_max；较高利率判断依据）</t>
+          <t>对外担保（相关还款责任）五级分类非正常余额（万元）</t>
         </is>
       </c>
       <c r="H366" s="6" t="inlineStr"/>
@@ -14352,7 +14358,7 @@
       </c>
       <c r="C367" s="6" t="inlineStr">
         <is>
-          <t>guaranteeAbnormalBal</t>
+          <t>extendBal</t>
         </is>
       </c>
       <c r="D367" s="6" t="inlineStr">
@@ -14364,7 +14370,7 @@
       <c r="F367" s="6" t="inlineStr"/>
       <c r="G367" s="6" t="inlineStr">
         <is>
-          <t>对外担保（相关还款责任）五级分类非正常余额（万元）</t>
+          <t>展期债务余额（万元）</t>
         </is>
       </c>
       <c r="H367" s="6" t="inlineStr"/>
@@ -14385,7 +14391,7 @@
       </c>
       <c r="C368" s="6" t="inlineStr">
         <is>
-          <t>extendBal</t>
+          <t>delayBal</t>
         </is>
       </c>
       <c r="D368" s="6" t="inlineStr">
@@ -14397,7 +14403,7 @@
       <c r="F368" s="6" t="inlineStr"/>
       <c r="G368" s="6" t="inlineStr">
         <is>
-          <t>展期债务余额（万元）</t>
+          <t>落实金融困等政策银行主动延期债务余额（万元）</t>
         </is>
       </c>
       <c r="H368" s="6" t="inlineStr"/>
@@ -14418,7 +14424,7 @@
       </c>
       <c r="C369" s="6" t="inlineStr">
         <is>
-          <t>delayBal</t>
+          <t>creditAbnormalBal</t>
         </is>
       </c>
       <c r="D369" s="6" t="inlineStr">
@@ -14430,7 +14436,7 @@
       <c r="F369" s="6" t="inlineStr"/>
       <c r="G369" s="6" t="inlineStr">
         <is>
-          <t>落实金融困等政策银行主动延期债务余额（万元）</t>
+          <t>未结清信贷五级分类非正常余额（万元）</t>
         </is>
       </c>
       <c r="H369" s="6" t="inlineStr"/>
@@ -14451,7 +14457,7 @@
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>creditAbnormalBal</t>
+          <t>acctAbnormalBal</t>
         </is>
       </c>
       <c r="D370" s="6" t="inlineStr">
@@ -14463,7 +14469,7 @@
       <c r="F370" s="6" t="inlineStr"/>
       <c r="G370" s="6" t="inlineStr">
         <is>
-          <t>未结清信贷五级分类非正常余额（万元）</t>
+          <t>未结清账户状态非正常余额（万元）</t>
         </is>
       </c>
       <c r="H370" s="6" t="inlineStr"/>
@@ -14484,7 +14490,7 @@
       </c>
       <c r="C371" s="6" t="inlineStr">
         <is>
-          <t>acctAbnormalBal</t>
+          <t>cardAbnormalBal</t>
         </is>
       </c>
       <c r="D371" s="6" t="inlineStr">
@@ -14496,7 +14502,7 @@
       <c r="F371" s="6" t="inlineStr"/>
       <c r="G371" s="6" t="inlineStr">
         <is>
-          <t>未结清账户状态非正常余额（万元）</t>
+          <t>未销户贷记卡账户状态非正常余额（万元）</t>
         </is>
       </c>
       <c r="H371" s="6" t="inlineStr"/>
@@ -14517,7 +14523,7 @@
       </c>
       <c r="C372" s="6" t="inlineStr">
         <is>
-          <t>cardAbnormalBal</t>
+          <t>guaranteeHkAbnormalBal</t>
         </is>
       </c>
       <c r="D372" s="6" t="inlineStr">
@@ -14529,7 +14535,7 @@
       <c r="F372" s="6" t="inlineStr"/>
       <c r="G372" s="6" t="inlineStr">
         <is>
-          <t>未销户贷记卡账户状态非正常余额（万元）</t>
+          <t>对外担保（相关还款责任）还款状态非正常余额（万元）</t>
         </is>
       </c>
       <c r="H372" s="6" t="inlineStr"/>
@@ -14550,7 +14556,7 @@
       </c>
       <c r="C373" s="6" t="inlineStr">
         <is>
-          <t>guaranteeHkAbnormalBal</t>
+          <t>creditUseRate</t>
         </is>
       </c>
       <c r="D373" s="6" t="inlineStr">
@@ -14562,7 +14568,7 @@
       <c r="F373" s="6" t="inlineStr"/>
       <c r="G373" s="6" t="inlineStr">
         <is>
-          <t>对外担保（相关还款责任）还款状态非正常余额（万元）</t>
+          <t>信用卡使用率（%）</t>
         </is>
       </c>
       <c r="H373" s="6" t="inlineStr"/>
@@ -14571,37 +14577,31 @@
       <c r="K373" s="8" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="6" t="inlineStr">
+      <c r="A374" t="inlineStr">
         <is>
           <t>app_guarantor_credit_info</t>
         </is>
       </c>
-      <c r="B374" s="6" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>担保人征信表</t>
         </is>
       </c>
-      <c r="C374" s="6" t="inlineStr">
-        <is>
-          <t>creditUseRate</t>
-        </is>
-      </c>
-      <c r="D374" s="6" t="inlineStr">
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>nonBankLiabTotal</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
         <is>
           <t>DECIMAL</t>
         </is>
       </c>
-      <c r="E374" s="6" t="inlineStr"/>
-      <c r="F374" s="6" t="inlineStr"/>
-      <c r="G374" s="6" t="inlineStr">
-        <is>
-          <t>信用卡使用率（%）</t>
-        </is>
-      </c>
-      <c r="H374" s="6" t="inlineStr"/>
-      <c r="I374" s="6" t="inlineStr"/>
-      <c r="J374" s="8" t="n"/>
-      <c r="K374" s="8" t="n"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>在非银机构负债合计（万元，个人，上游直给：gr_fyjg_liab_tot）</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -14616,17 +14616,17 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>nonBankLiabTotal</t>
+          <t>loanQuery12m</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>在非银机构负债合计（万元，个人，上游直给：gr_fyjg_liab_tot）</t>
+          <t>近一年贷款审批征信查询次数（2026-09-03 新增）</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>loanQuery12m</t>
+          <t>loanQuery6m</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -14653,7 +14653,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>近一年贷款审批征信查询次数（2026-09-03 新增）</t>
+          <t>近6个月贷款审批征信查询次数（2026-09-03 新增）</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>loanQuery6m</t>
+          <t>loanQuery3m</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -14680,7 +14680,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>近6个月贷款审批征信查询次数（2026-09-03 新增）</t>
+          <t>近3个月贷款审批征信查询次数（2026-09-03 新增）</t>
         </is>
       </c>
     </row>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>loanQuery3m</t>
+          <t>cardQuery12m</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>近3个月贷款审批征信查询次数（2026-09-03 新增）</t>
+          <t>近一年信用卡审批征信查询次数（2026-09-03 新增）</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>cardQuery12m</t>
+          <t>cardQuery6m</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>近一年信用卡审批征信查询次数（2026-09-03 新增）</t>
+          <t>近6个月信用卡审批征信查询次数（2026-09-03 新增）</t>
         </is>
       </c>
     </row>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>cardQuery6m</t>
+          <t>cardQuery3m</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>近6个月信用卡审批征信查询次数（2026-09-03 新增）</t>
+          <t>近3个月信用卡审批征信查询次数（2026-09-03 新增）</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>cardQuery3m</t>
+          <t>selfQuery1m</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -14788,71 +14788,85 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>近3个月信用卡审批征信查询次数（2026-09-03 新增）</t>
+          <t>近1个月本人查询征信查询次数（2026-09-03 新增）</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
+      <c r="A382" s="6" t="inlineStr">
         <is>
           <t>app_guarantor_credit_info</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B382" s="6" t="inlineStr">
         <is>
           <t>担保人征信表</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>selfQuery1m</t>
-        </is>
-      </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>近1个月本人查询征信查询次数（2026-09-03 新增）</t>
-        </is>
-      </c>
+      <c r="C382" s="6" t="inlineStr">
+        <is>
+          <t>inputtime</t>
+        </is>
+      </c>
+      <c r="D382" s="6" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E382" s="6" t="inlineStr"/>
+      <c r="F382" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G382" s="6" t="inlineStr">
+        <is>
+          <t>入库时间</t>
+        </is>
+      </c>
+      <c r="H382" s="6" t="inlineStr"/>
+      <c r="I382" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J382" s="8" t="n"/>
+      <c r="K382" s="8" t="n"/>
     </row>
     <row r="383">
-      <c r="A383" s="6" t="inlineStr">
-        <is>
-          <t>app_guarantor_credit_info</t>
-        </is>
-      </c>
-      <c r="B383" s="6" t="inlineStr">
-        <is>
-          <t>担保人征信表</t>
-        </is>
-      </c>
-      <c r="C383" s="6" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D383" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E383" s="6" t="inlineStr"/>
-      <c r="F383" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G383" s="6" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H383" s="6" t="inlineStr"/>
-      <c r="I383" s="6" t="inlineStr">
+      <c r="A383" s="9" t="inlineStr">
+        <is>
+          <t>app_credit_query_info</t>
+        </is>
+      </c>
+      <c r="B383" s="9" t="inlineStr">
+        <is>
+          <t>征信查询次数表</t>
+        </is>
+      </c>
+      <c r="C383" s="9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D383" s="9" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E383" s="9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F383" s="9" t="inlineStr"/>
+      <c r="G383" s="9" t="inlineStr"/>
+      <c r="H383" s="9" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I383" s="9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -14861,44 +14875,52 @@
       <c r="K383" s="8" t="n"/>
     </row>
     <row r="384">
-      <c r="A384" s="9" t="inlineStr">
+      <c r="A384" s="10" t="inlineStr">
         <is>
           <t>app_credit_query_info</t>
         </is>
       </c>
-      <c r="B384" s="9" t="inlineStr">
+      <c r="B384" s="10" t="inlineStr">
         <is>
           <t>征信查询次数表</t>
         </is>
       </c>
-      <c r="C384" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D384" s="9" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E384" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F384" s="9" t="inlineStr"/>
-      <c r="G384" s="9" t="inlineStr"/>
-      <c r="H384" s="9" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I384" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J384" s="8" t="n"/>
+      <c r="C384" s="10" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D384" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E384" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F384" s="10" t="inlineStr"/>
+      <c r="G384" s="10" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H384" s="10" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I384" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J384" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K384" s="8" t="n"/>
     </row>
     <row r="385">
@@ -14914,7 +14936,7 @@
       </c>
       <c r="C385" s="10" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D385" s="10" t="inlineStr">
@@ -14922,15 +14944,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E385" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E385" s="10" t="inlineStr"/>
       <c r="F385" s="10" t="inlineStr"/>
       <c r="G385" s="10" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H385" s="10" t="inlineStr">
@@ -14963,74 +14981,56 @@
       </c>
       <c r="C386" s="10" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D386" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E386" s="10" t="inlineStr"/>
       <c r="F386" s="10" t="inlineStr"/>
       <c r="G386" s="10" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H386" s="10" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H386" s="10" t="inlineStr"/>
       <c r="I386" s="10" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J386" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J386" s="8" t="n"/>
       <c r="K386" s="8" t="n"/>
     </row>
     <row r="387">
-      <c r="A387" s="10" t="inlineStr">
+      <c r="A387" t="inlineStr">
         <is>
           <t>app_credit_query_info</t>
         </is>
       </c>
-      <c r="B387" s="10" t="inlineStr">
+      <c r="B387" t="inlineStr">
         <is>
           <t>征信查询次数表</t>
         </is>
       </c>
-      <c r="C387" s="10" t="inlineStr">
-        <is>
-          <t>customerName</t>
-        </is>
-      </c>
-      <c r="D387" s="10" t="inlineStr">
-        <is>
-          <t>VARCHAR(128)</t>
-        </is>
-      </c>
-      <c r="E387" s="10" t="inlineStr"/>
-      <c r="F387" s="10" t="inlineStr"/>
-      <c r="G387" s="10" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="H387" s="10" t="inlineStr"/>
-      <c r="I387" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J387" s="8" t="n"/>
-      <c r="K387" s="8" t="n"/>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>guarantorId</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>担保人客户编号</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -15045,115 +15045,121 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>guarantorId</t>
+          <t>guarantorName</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>担保人客户编号</t>
+          <t>担保人名称</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
+      <c r="A389" s="10" t="inlineStr">
         <is>
           <t>app_credit_query_info</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B389" s="10" t="inlineStr">
         <is>
           <t>征信查询次数表</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
-        <is>
-          <t>guarantorName</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
+      <c r="C389" s="10" t="inlineStr">
+        <is>
+          <t>queryTime</t>
+        </is>
+      </c>
+      <c r="D389" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(32)</t>
+        </is>
+      </c>
+      <c r="E389" s="10" t="inlineStr"/>
+      <c r="F389" s="10" t="inlineStr"/>
+      <c r="G389" s="10" t="inlineStr">
+        <is>
+          <t>征信查询时间</t>
+        </is>
+      </c>
+      <c r="H389" s="10" t="inlineStr"/>
+      <c r="I389" s="10" t="inlineStr"/>
+      <c r="J389" s="8" t="n"/>
+      <c r="K389" s="8" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="17" t="inlineStr">
+        <is>
+          <t>app_credit_query_info</t>
+        </is>
+      </c>
+      <c r="B390" s="17" t="inlineStr">
+        <is>
+          <t>征信查询次数表</t>
+        </is>
+      </c>
+      <c r="C390" s="17" t="inlineStr">
+        <is>
+          <t>zxReportNo</t>
+        </is>
+      </c>
+      <c r="D390" s="17" t="inlineStr">
         <is>
           <t>VARCHAR(128)</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>担保人名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="10" t="inlineStr">
+      <c r="E390" s="17" t="n"/>
+      <c r="F390" s="17" t="n"/>
+      <c r="G390" s="17" t="inlineStr">
+        <is>
+          <t>征信报告记录号</t>
+        </is>
+      </c>
+      <c r="H390" s="17" t="n"/>
+      <c r="I390" s="17" t="n"/>
+      <c r="J390" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K390" s="8" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="10" t="inlineStr">
         <is>
           <t>app_credit_query_info</t>
         </is>
       </c>
-      <c r="B390" s="10" t="inlineStr">
+      <c r="B391" s="10" t="inlineStr">
         <is>
           <t>征信查询次数表</t>
         </is>
       </c>
-      <c r="C390" s="10" t="inlineStr">
-        <is>
-          <t>queryTime</t>
-        </is>
-      </c>
-      <c r="D390" s="10" t="inlineStr">
-        <is>
-          <t>VARCHAR(32)</t>
-        </is>
-      </c>
-      <c r="E390" s="10" t="inlineStr"/>
-      <c r="F390" s="10" t="inlineStr"/>
-      <c r="G390" s="10" t="inlineStr">
-        <is>
-          <t>征信查询时间</t>
-        </is>
-      </c>
-      <c r="H390" s="10" t="inlineStr"/>
-      <c r="I390" s="10" t="inlineStr"/>
-      <c r="J390" s="8" t="n"/>
-      <c r="K390" s="8" t="n"/>
-    </row>
-    <row r="391">
-      <c r="A391" s="17" t="inlineStr">
-        <is>
-          <t>app_credit_query_info</t>
-        </is>
-      </c>
-      <c r="B391" s="17" t="inlineStr">
-        <is>
-          <t>征信查询次数表</t>
-        </is>
-      </c>
-      <c r="C391" s="17" t="inlineStr">
-        <is>
-          <t>zxReportNo</t>
-        </is>
-      </c>
-      <c r="D391" s="17" t="inlineStr">
-        <is>
-          <t>VARCHAR(128)</t>
-        </is>
-      </c>
-      <c r="E391" s="17" t="n"/>
-      <c r="F391" s="17" t="n"/>
-      <c r="G391" s="17" t="inlineStr">
-        <is>
-          <t>征信报告记录号</t>
-        </is>
-      </c>
-      <c r="H391" s="17" t="n"/>
-      <c r="I391" s="17" t="n"/>
-      <c r="J391" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="C391" s="10" t="inlineStr">
+        <is>
+          <t>loanQuery12m</t>
+        </is>
+      </c>
+      <c r="D391" s="10" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="E391" s="10" t="inlineStr"/>
+      <c r="F391" s="10" t="inlineStr"/>
+      <c r="G391" s="10" t="inlineStr">
+        <is>
+          <t>近一年贷款审批征信查询次数</t>
+        </is>
+      </c>
+      <c r="H391" s="10" t="inlineStr"/>
+      <c r="I391" s="10" t="inlineStr"/>
+      <c r="J391" s="8" t="n"/>
       <c r="K391" s="8" t="n"/>
     </row>
     <row r="392">
@@ -15169,7 +15175,7 @@
       </c>
       <c r="C392" s="10" t="inlineStr">
         <is>
-          <t>loanQuery12m</t>
+          <t>loanQuery6m</t>
         </is>
       </c>
       <c r="D392" s="10" t="inlineStr">
@@ -15181,7 +15187,7 @@
       <c r="F392" s="10" t="inlineStr"/>
       <c r="G392" s="10" t="inlineStr">
         <is>
-          <t>近一年贷款审批征信查询次数</t>
+          <t>近6个月贷款审批征信查询次数</t>
         </is>
       </c>
       <c r="H392" s="10" t="inlineStr"/>
@@ -15202,7 +15208,7 @@
       </c>
       <c r="C393" s="10" t="inlineStr">
         <is>
-          <t>loanQuery6m</t>
+          <t>loanQuery3m</t>
         </is>
       </c>
       <c r="D393" s="10" t="inlineStr">
@@ -15214,7 +15220,7 @@
       <c r="F393" s="10" t="inlineStr"/>
       <c r="G393" s="10" t="inlineStr">
         <is>
-          <t>近6个月贷款审批征信查询次数</t>
+          <t>近3个月贷款审批征信查询次数</t>
         </is>
       </c>
       <c r="H393" s="10" t="inlineStr"/>
@@ -15235,7 +15241,7 @@
       </c>
       <c r="C394" s="10" t="inlineStr">
         <is>
-          <t>loanQuery3m</t>
+          <t>cardQuery12m</t>
         </is>
       </c>
       <c r="D394" s="10" t="inlineStr">
@@ -15247,7 +15253,7 @@
       <c r="F394" s="10" t="inlineStr"/>
       <c r="G394" s="10" t="inlineStr">
         <is>
-          <t>近3个月贷款审批征信查询次数</t>
+          <t>近一年信用卡审批征信查询次数</t>
         </is>
       </c>
       <c r="H394" s="10" t="inlineStr"/>
@@ -15268,7 +15274,7 @@
       </c>
       <c r="C395" s="10" t="inlineStr">
         <is>
-          <t>cardQuery12m</t>
+          <t>cardQuery6m</t>
         </is>
       </c>
       <c r="D395" s="10" t="inlineStr">
@@ -15280,7 +15286,7 @@
       <c r="F395" s="10" t="inlineStr"/>
       <c r="G395" s="10" t="inlineStr">
         <is>
-          <t>近一年信用卡审批征信查询次数</t>
+          <t>近6个月信用卡审批征信查询次数</t>
         </is>
       </c>
       <c r="H395" s="10" t="inlineStr"/>
@@ -15301,7 +15307,7 @@
       </c>
       <c r="C396" s="10" t="inlineStr">
         <is>
-          <t>cardQuery6m</t>
+          <t>cardQuery3m</t>
         </is>
       </c>
       <c r="D396" s="10" t="inlineStr">
@@ -15313,7 +15319,7 @@
       <c r="F396" s="10" t="inlineStr"/>
       <c r="G396" s="10" t="inlineStr">
         <is>
-          <t>近6个月信用卡审批征信查询次数</t>
+          <t>近3个月信用卡审批征信查询次数</t>
         </is>
       </c>
       <c r="H396" s="10" t="inlineStr"/>
@@ -15334,7 +15340,7 @@
       </c>
       <c r="C397" s="10" t="inlineStr">
         <is>
-          <t>cardQuery3m</t>
+          <t>selfQuery1m</t>
         </is>
       </c>
       <c r="D397" s="10" t="inlineStr">
@@ -15346,7 +15352,7 @@
       <c r="F397" s="10" t="inlineStr"/>
       <c r="G397" s="10" t="inlineStr">
         <is>
-          <t>近3个月信用卡审批征信查询次数</t>
+          <t>近1个月本人查询征信查询次数</t>
         </is>
       </c>
       <c r="H397" s="10" t="inlineStr"/>
@@ -15367,60 +15373,68 @@
       </c>
       <c r="C398" s="10" t="inlineStr">
         <is>
-          <t>selfQuery1m</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D398" s="10" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E398" s="10" t="inlineStr"/>
-      <c r="F398" s="10" t="inlineStr"/>
+      <c r="F398" s="10" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G398" s="10" t="inlineStr">
         <is>
-          <t>近1个月本人查询征信查询次数</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H398" s="10" t="inlineStr"/>
-      <c r="I398" s="10" t="inlineStr"/>
+      <c r="I398" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J398" s="8" t="n"/>
       <c r="K398" s="8" t="n"/>
     </row>
     <row r="399">
-      <c r="A399" s="10" t="inlineStr">
-        <is>
-          <t>app_credit_query_info</t>
-        </is>
-      </c>
-      <c r="B399" s="10" t="inlineStr">
-        <is>
-          <t>征信查询次数表</t>
-        </is>
-      </c>
-      <c r="C399" s="10" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D399" s="10" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E399" s="10" t="inlineStr"/>
-      <c r="F399" s="10" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G399" s="10" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H399" s="10" t="inlineStr"/>
-      <c r="I399" s="10" t="inlineStr">
+      <c r="A399" s="11" t="inlineStr">
+        <is>
+          <t>app_capital_flow_info</t>
+        </is>
+      </c>
+      <c r="B399" s="11" t="inlineStr">
+        <is>
+          <t>资金回流/用途异常表</t>
+        </is>
+      </c>
+      <c r="C399" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D399" s="11" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E399" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F399" s="11" t="inlineStr"/>
+      <c r="G399" s="11" t="inlineStr"/>
+      <c r="H399" s="11" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I399" s="11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -15429,44 +15443,52 @@
       <c r="K399" s="8" t="n"/>
     </row>
     <row r="400">
-      <c r="A400" s="11" t="inlineStr">
+      <c r="A400" s="12" t="inlineStr">
         <is>
           <t>app_capital_flow_info</t>
         </is>
       </c>
-      <c r="B400" s="11" t="inlineStr">
+      <c r="B400" s="12" t="inlineStr">
         <is>
           <t>资金回流/用途异常表</t>
         </is>
       </c>
-      <c r="C400" s="11" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D400" s="11" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E400" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F400" s="11" t="inlineStr"/>
-      <c r="G400" s="11" t="inlineStr"/>
-      <c r="H400" s="11" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I400" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J400" s="8" t="n"/>
+      <c r="C400" s="12" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D400" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E400" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F400" s="12" t="inlineStr"/>
+      <c r="G400" s="12" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H400" s="12" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I400" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J400" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K400" s="8" t="n"/>
     </row>
     <row r="401">
@@ -15482,7 +15504,7 @@
       </c>
       <c r="C401" s="12" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D401" s="12" t="inlineStr">
@@ -15490,15 +15512,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E401" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E401" s="12" t="inlineStr"/>
       <c r="F401" s="12" t="inlineStr"/>
       <c r="G401" s="12" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H401" s="12" t="inlineStr">
@@ -15531,52 +15549,44 @@
       </c>
       <c r="C402" s="12" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D402" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E402" s="12" t="inlineStr"/>
       <c r="F402" s="12" t="inlineStr"/>
       <c r="G402" s="12" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H402" s="12" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H402" s="12" t="inlineStr"/>
       <c r="I402" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J402" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J402" s="8" t="n"/>
       <c r="K402" s="8" t="n"/>
     </row>
     <row r="403">
-      <c r="A403" s="12" t="inlineStr">
+      <c r="A403" s="17" t="inlineStr">
         <is>
           <t>app_capital_flow_info</t>
         </is>
       </c>
-      <c r="B403" s="12" t="inlineStr">
+      <c r="B403" s="17" t="inlineStr">
         <is>
           <t>资金回流/用途异常表</t>
         </is>
       </c>
-      <c r="C403" s="12" t="inlineStr">
-        <is>
-          <t>customerName</t>
+      <c r="C403" s="17" t="inlineStr">
+        <is>
+          <t>serialNo</t>
         </is>
       </c>
       <c r="D403" s="12" t="inlineStr">
@@ -15584,57 +15594,53 @@
           <t>VARCHAR(128)</t>
         </is>
       </c>
-      <c r="E403" s="12" t="inlineStr"/>
-      <c r="F403" s="12" t="inlineStr"/>
-      <c r="G403" s="12" t="inlineStr">
-        <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="H403" s="12" t="inlineStr"/>
-      <c r="I403" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J403" s="8" t="n"/>
+      <c r="E403" s="17" t="n"/>
+      <c r="F403" s="17" t="n"/>
+      <c r="G403" s="17" t="inlineStr">
+        <is>
+          <t>流水号</t>
+        </is>
+      </c>
+      <c r="H403" s="17" t="n"/>
+      <c r="I403" s="17" t="n"/>
+      <c r="J403" s="24" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K403" s="8" t="n"/>
     </row>
     <row r="404">
-      <c r="A404" s="17" t="inlineStr">
+      <c r="A404" s="12" t="inlineStr">
         <is>
           <t>app_capital_flow_info</t>
         </is>
       </c>
-      <c r="B404" s="17" t="inlineStr">
+      <c r="B404" s="12" t="inlineStr">
         <is>
           <t>资金回流/用途异常表</t>
         </is>
       </c>
-      <c r="C404" s="17" t="inlineStr">
-        <is>
-          <t>serialNo</t>
+      <c r="C404" s="12" t="inlineStr">
+        <is>
+          <t>loanSerialNo</t>
         </is>
       </c>
       <c r="D404" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
-        </is>
-      </c>
-      <c r="E404" s="17" t="n"/>
-      <c r="F404" s="17" t="n"/>
-      <c r="G404" s="17" t="inlineStr">
-        <is>
-          <t>流水号</t>
-        </is>
-      </c>
-      <c r="H404" s="17" t="n"/>
-      <c r="I404" s="17" t="n"/>
-      <c r="J404" s="24" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E404" s="12" t="inlineStr"/>
+      <c r="F404" s="12" t="inlineStr"/>
+      <c r="G404" s="12" t="inlineStr">
+        <is>
+          <t>借据号</t>
+        </is>
+      </c>
+      <c r="H404" s="12" t="inlineStr"/>
+      <c r="I404" s="12" t="inlineStr"/>
+      <c r="J404" s="8" t="n"/>
       <c r="K404" s="8" t="n"/>
     </row>
     <row r="405">
@@ -15650,7 +15656,7 @@
       </c>
       <c r="C405" s="12" t="inlineStr">
         <is>
-          <t>loanSerialNo</t>
+          <t>capitalCheckTaskType</t>
         </is>
       </c>
       <c r="D405" s="12" t="inlineStr">
@@ -15662,13 +15668,17 @@
       <c r="F405" s="12" t="inlineStr"/>
       <c r="G405" s="12" t="inlineStr">
         <is>
-          <t>借据号</t>
+          <t>任务类型（码值：资金用途检查任务类型（码值待确认））</t>
         </is>
       </c>
       <c r="H405" s="12" t="inlineStr"/>
       <c r="I405" s="12" t="inlineStr"/>
       <c r="J405" s="8" t="n"/>
-      <c r="K405" s="8" t="n"/>
+      <c r="K405" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="12" t="inlineStr">
@@ -15683,7 +15693,7 @@
       </c>
       <c r="C406" s="12" t="inlineStr">
         <is>
-          <t>capitalCheckTaskType</t>
+          <t>approveStatus</t>
         </is>
       </c>
       <c r="D406" s="12" t="inlineStr">
@@ -15695,7 +15705,7 @@
       <c r="F406" s="12" t="inlineStr"/>
       <c r="G406" s="12" t="inlineStr">
         <is>
-          <t>任务类型（码值：资金用途检查任务类型（码值待确认））</t>
+          <t>审批状态（码值：审批通过/待审批/驳回（码值待确认））</t>
         </is>
       </c>
       <c r="H406" s="12" t="inlineStr"/>
@@ -15720,7 +15730,7 @@
       </c>
       <c r="C407" s="12" t="inlineStr">
         <is>
-          <t>approveStatus</t>
+          <t>isPurposeAbnormal</t>
         </is>
       </c>
       <c r="D407" s="12" t="inlineStr">
@@ -15732,17 +15742,13 @@
       <c r="F407" s="12" t="inlineStr"/>
       <c r="G407" s="12" t="inlineStr">
         <is>
-          <t>审批状态（码值：审批通过/待审批/驳回（码值待确认））</t>
+          <t>是否回流异常（码值：是/否）</t>
         </is>
       </c>
       <c r="H407" s="12" t="inlineStr"/>
       <c r="I407" s="12" t="inlineStr"/>
       <c r="J407" s="8" t="n"/>
-      <c r="K407" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K407" s="8" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="12" t="inlineStr">
@@ -15757,19 +15763,19 @@
       </c>
       <c r="C408" s="12" t="inlineStr">
         <is>
-          <t>isPurposeAbnormal</t>
+          <t>rectificationSituation</t>
         </is>
       </c>
       <c r="D408" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E408" s="12" t="inlineStr"/>
       <c r="F408" s="12" t="inlineStr"/>
       <c r="G408" s="12" t="inlineStr">
         <is>
-          <t>是否回流异常（码值：是/否）</t>
+          <t>整改情况</t>
         </is>
       </c>
       <c r="H408" s="12" t="inlineStr"/>
@@ -15790,19 +15796,19 @@
       </c>
       <c r="C409" s="12" t="inlineStr">
         <is>
-          <t>rectificationSituation</t>
+          <t>rectificationDeadline</t>
         </is>
       </c>
       <c r="D409" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E409" s="12" t="inlineStr"/>
       <c r="F409" s="12" t="inlineStr"/>
       <c r="G409" s="12" t="inlineStr">
         <is>
-          <t>整改情况</t>
+          <t>整改期限</t>
         </is>
       </c>
       <c r="H409" s="12" t="inlineStr"/>
@@ -15823,19 +15829,19 @@
       </c>
       <c r="C410" s="12" t="inlineStr">
         <is>
-          <t>rectificationDeadline</t>
+          <t>rectificationExplanation</t>
         </is>
       </c>
       <c r="D410" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E410" s="12" t="inlineStr"/>
       <c r="F410" s="12" t="inlineStr"/>
       <c r="G410" s="12" t="inlineStr">
         <is>
-          <t>整改期限</t>
+          <t>整改情况说明</t>
         </is>
       </c>
       <c r="H410" s="12" t="inlineStr"/>
@@ -15856,7 +15862,7 @@
       </c>
       <c r="C411" s="12" t="inlineStr">
         <is>
-          <t>rectificationExplanation</t>
+          <t>identifyReason</t>
         </is>
       </c>
       <c r="D411" s="12" t="inlineStr">
@@ -15868,7 +15874,7 @@
       <c r="F411" s="12" t="inlineStr"/>
       <c r="G411" s="12" t="inlineStr">
         <is>
-          <t>整改情况说明</t>
+          <t>认定理由</t>
         </is>
       </c>
       <c r="H411" s="12" t="inlineStr"/>
@@ -15889,60 +15895,68 @@
       </c>
       <c r="C412" s="12" t="inlineStr">
         <is>
-          <t>identifyReason</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D412" s="12" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E412" s="12" t="inlineStr"/>
-      <c r="F412" s="12" t="inlineStr"/>
+      <c r="F412" s="12" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G412" s="12" t="inlineStr">
         <is>
-          <t>认定理由</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H412" s="12" t="inlineStr"/>
-      <c r="I412" s="12" t="inlineStr"/>
+      <c r="I412" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J412" s="8" t="n"/>
       <c r="K412" s="8" t="n"/>
     </row>
     <row r="413">
-      <c r="A413" s="12" t="inlineStr">
-        <is>
-          <t>app_capital_flow_info</t>
-        </is>
-      </c>
-      <c r="B413" s="12" t="inlineStr">
-        <is>
-          <t>资金回流/用途异常表</t>
-        </is>
-      </c>
-      <c r="C413" s="12" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D413" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E413" s="12" t="inlineStr"/>
-      <c r="F413" s="12" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G413" s="12" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H413" s="12" t="inlineStr"/>
-      <c r="I413" s="12" t="inlineStr">
+      <c r="A413" s="13" t="inlineStr">
+        <is>
+          <t>app_entrust_pay_info</t>
+        </is>
+      </c>
+      <c r="B413" s="13" t="inlineStr">
+        <is>
+          <t>受托支付明细表</t>
+        </is>
+      </c>
+      <c r="C413" s="13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D413" s="13" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E413" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F413" s="13" t="inlineStr"/>
+      <c r="G413" s="13" t="inlineStr"/>
+      <c r="H413" s="13" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I413" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -15951,44 +15965,52 @@
       <c r="K413" s="8" t="n"/>
     </row>
     <row r="414">
-      <c r="A414" s="13" t="inlineStr">
+      <c r="A414" s="14" t="inlineStr">
         <is>
           <t>app_entrust_pay_info</t>
         </is>
       </c>
-      <c r="B414" s="13" t="inlineStr">
+      <c r="B414" s="14" t="inlineStr">
         <is>
           <t>受托支付明细表</t>
         </is>
       </c>
-      <c r="C414" s="13" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D414" s="13" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E414" s="13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F414" s="13" t="inlineStr"/>
-      <c r="G414" s="13" t="inlineStr"/>
-      <c r="H414" s="13" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I414" s="13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J414" s="8" t="n"/>
+      <c r="C414" s="14" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D414" s="14" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E414" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F414" s="14" t="inlineStr"/>
+      <c r="G414" s="14" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H414" s="14" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I414" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J414" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K414" s="8" t="n"/>
     </row>
     <row r="415">
@@ -16004,7 +16026,7 @@
       </c>
       <c r="C415" s="14" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D415" s="14" t="inlineStr">
@@ -16012,15 +16034,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E415" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E415" s="14" t="inlineStr"/>
       <c r="F415" s="14" t="inlineStr"/>
       <c r="G415" s="14" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H415" s="14" t="inlineStr">
@@ -16053,36 +16071,28 @@
       </c>
       <c r="C416" s="14" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D416" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E416" s="14" t="inlineStr"/>
       <c r="F416" s="14" t="inlineStr"/>
       <c r="G416" s="14" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H416" s="14" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H416" s="14" t="inlineStr"/>
       <c r="I416" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J416" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J416" s="8" t="n"/>
       <c r="K416" s="8" t="n"/>
     </row>
     <row r="417">
@@ -16098,29 +16108,29 @@
       </c>
       <c r="C417" s="14" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>paymentMode</t>
         </is>
       </c>
       <c r="D417" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E417" s="14" t="inlineStr"/>
       <c r="F417" s="14" t="inlineStr"/>
       <c r="G417" s="14" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>支付方式（码值：受托支付/自主支付，码值待确认）</t>
         </is>
       </c>
       <c r="H417" s="14" t="inlineStr"/>
-      <c r="I417" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="I417" s="14" t="inlineStr"/>
       <c r="J417" s="8" t="n"/>
-      <c r="K417" s="8" t="n"/>
+      <c r="K417" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="418" ht="28" customHeight="1" s="25">
       <c r="A418" s="14" t="inlineStr">
@@ -16135,29 +16145,25 @@
       </c>
       <c r="C418" s="14" t="inlineStr">
         <is>
-          <t>paymentMode</t>
+          <t>payDate</t>
         </is>
       </c>
       <c r="D418" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E418" s="14" t="inlineStr"/>
       <c r="F418" s="14" t="inlineStr"/>
       <c r="G418" s="14" t="inlineStr">
         <is>
-          <t>支付方式（码值：受托支付/自主支付，码值待确认）</t>
+          <t>支付日期</t>
         </is>
       </c>
       <c r="H418" s="14" t="inlineStr"/>
       <c r="I418" s="14" t="inlineStr"/>
       <c r="J418" s="8" t="n"/>
-      <c r="K418" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K418" s="8" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="14" t="inlineStr">
@@ -16172,24 +16178,28 @@
       </c>
       <c r="C419" s="14" t="inlineStr">
         <is>
-          <t>payDate</t>
+          <t>accountName</t>
         </is>
       </c>
       <c r="D419" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E419" s="14" t="inlineStr"/>
       <c r="F419" s="14" t="inlineStr"/>
       <c r="G419" s="14" t="inlineStr">
         <is>
-          <t>支付日期</t>
+          <t>收款人名称</t>
         </is>
       </c>
       <c r="H419" s="14" t="inlineStr"/>
       <c r="I419" s="14" t="inlineStr"/>
-      <c r="J419" s="8" t="n"/>
+      <c r="J419" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K419" s="8" t="n"/>
     </row>
     <row r="420">
@@ -16205,64 +16215,68 @@
       </c>
       <c r="C420" s="14" t="inlineStr">
         <is>
-          <t>accountName</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D420" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E420" s="14" t="inlineStr"/>
-      <c r="F420" s="14" t="inlineStr"/>
+      <c r="F420" s="14" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G420" s="14" t="inlineStr">
         <is>
-          <t>收款人名称</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H420" s="14" t="inlineStr"/>
-      <c r="I420" s="14" t="inlineStr"/>
-      <c r="J420" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="I420" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J420" s="8" t="n"/>
       <c r="K420" s="8" t="n"/>
     </row>
     <row r="421">
-      <c r="A421" s="14" t="inlineStr">
-        <is>
-          <t>app_entrust_pay_info</t>
-        </is>
-      </c>
-      <c r="B421" s="14" t="inlineStr">
-        <is>
-          <t>受托支付明细表</t>
-        </is>
-      </c>
-      <c r="C421" s="14" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D421" s="14" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E421" s="14" t="inlineStr"/>
-      <c r="F421" s="14" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G421" s="14" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H421" s="14" t="inlineStr"/>
-      <c r="I421" s="14" t="inlineStr">
+      <c r="A421" s="15" t="inlineStr">
+        <is>
+          <t>app_settle_counterparty_info</t>
+        </is>
+      </c>
+      <c r="B421" s="15" t="inlineStr">
+        <is>
+          <t>结算交易对手表</t>
+        </is>
+      </c>
+      <c r="C421" s="15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D421" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E421" s="15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F421" s="15" t="inlineStr"/>
+      <c r="G421" s="15" t="inlineStr"/>
+      <c r="H421" s="15" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I421" s="15" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -16271,44 +16285,52 @@
       <c r="K421" s="8" t="n"/>
     </row>
     <row r="422">
-      <c r="A422" s="15" t="inlineStr">
+      <c r="A422" s="16" t="inlineStr">
         <is>
           <t>app_settle_counterparty_info</t>
         </is>
       </c>
-      <c r="B422" s="15" t="inlineStr">
+      <c r="B422" s="16" t="inlineStr">
         <is>
           <t>结算交易对手表</t>
         </is>
       </c>
-      <c r="C422" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D422" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E422" s="15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F422" s="15" t="inlineStr"/>
-      <c r="G422" s="15" t="inlineStr"/>
-      <c r="H422" s="15" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I422" s="15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J422" s="8" t="n"/>
+      <c r="C422" s="16" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D422" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E422" s="16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F422" s="16" t="inlineStr"/>
+      <c r="G422" s="16" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H422" s="16" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I422" s="16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J422" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K422" s="8" t="n"/>
     </row>
     <row r="423">
@@ -16324,7 +16346,7 @@
       </c>
       <c r="C423" s="16" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D423" s="16" t="inlineStr">
@@ -16332,15 +16354,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E423" s="16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E423" s="16" t="inlineStr"/>
       <c r="F423" s="16" t="inlineStr"/>
       <c r="G423" s="16" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H423" s="16" t="inlineStr">
@@ -16373,36 +16391,28 @@
       </c>
       <c r="C424" s="16" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D424" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E424" s="16" t="inlineStr"/>
       <c r="F424" s="16" t="inlineStr"/>
       <c r="G424" s="16" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H424" s="16" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H424" s="16" t="inlineStr"/>
       <c r="I424" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J424" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J424" s="8" t="n"/>
       <c r="K424" s="8" t="n"/>
     </row>
     <row r="425">
@@ -16418,7 +16428,7 @@
       </c>
       <c r="C425" s="16" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>counterpartyName</t>
         </is>
       </c>
       <c r="D425" s="16" t="inlineStr">
@@ -16430,16 +16440,16 @@
       <c r="F425" s="16" t="inlineStr"/>
       <c r="G425" s="16" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>交易对手名称</t>
         </is>
       </c>
       <c r="H425" s="16" t="inlineStr"/>
-      <c r="I425" s="16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J425" s="8" t="n"/>
+      <c r="I425" s="16" t="inlineStr"/>
+      <c r="J425" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K425" s="8" t="n"/>
     </row>
     <row r="426">
@@ -16455,22 +16465,26 @@
       </c>
       <c r="C426" s="16" t="inlineStr">
         <is>
-          <t>counterpartyName</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="D426" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(16)</t>
         </is>
       </c>
       <c r="E426" s="16" t="inlineStr"/>
       <c r="F426" s="16" t="inlineStr"/>
       <c r="G426" s="16" t="inlineStr">
         <is>
-          <t>交易对手名称</t>
-        </is>
-      </c>
-      <c r="H426" s="16" t="inlineStr"/>
+          <t>方向（借方/贷方）</t>
+        </is>
+      </c>
+      <c r="H426" s="16" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
       <c r="I426" s="16" t="inlineStr"/>
       <c r="J426" s="8" t="inlineStr">
         <is>
@@ -16492,32 +16506,24 @@
       </c>
       <c r="C427" s="16" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="D427" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(16)</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="E427" s="16" t="inlineStr"/>
       <c r="F427" s="16" t="inlineStr"/>
       <c r="G427" s="16" t="inlineStr">
         <is>
-          <t>方向（借方/贷方）</t>
-        </is>
-      </c>
-      <c r="H427" s="16" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>发生额（万元）</t>
+        </is>
+      </c>
+      <c r="H427" s="16" t="inlineStr"/>
       <c r="I427" s="16" t="inlineStr"/>
-      <c r="J427" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J427" s="8" t="n"/>
       <c r="K427" s="8" t="n"/>
     </row>
     <row r="428">
@@ -16533,19 +16539,19 @@
       </c>
       <c r="C428" s="16" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>rankNo</t>
         </is>
       </c>
       <c r="D428" s="16" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>VARCHAR(16)</t>
         </is>
       </c>
       <c r="E428" s="16" t="inlineStr"/>
       <c r="F428" s="16" t="inlineStr"/>
       <c r="G428" s="16" t="inlineStr">
         <is>
-          <t>发生额（万元）</t>
+          <t>排名（TOP1-10）</t>
         </is>
       </c>
       <c r="H428" s="16" t="inlineStr"/>
@@ -16566,25 +16572,29 @@
       </c>
       <c r="C429" s="16" t="inlineStr">
         <is>
-          <t>rankNo</t>
+          <t>upstreamFlag</t>
         </is>
       </c>
       <c r="D429" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(16)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E429" s="16" t="inlineStr"/>
       <c r="F429" s="16" t="inlineStr"/>
       <c r="G429" s="16" t="inlineStr">
         <is>
-          <t>排名（TOP1-10）</t>
+          <t>是否前五大上游客户（码值：是/否）</t>
         </is>
       </c>
       <c r="H429" s="16" t="inlineStr"/>
       <c r="I429" s="16" t="inlineStr"/>
       <c r="J429" s="8" t="n"/>
-      <c r="K429" s="8" t="n"/>
+      <c r="K429" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="16" t="inlineStr">
@@ -16599,29 +16609,25 @@
       </c>
       <c r="C430" s="16" t="inlineStr">
         <is>
-          <t>upstreamFlag</t>
+          <t>remark</t>
         </is>
       </c>
       <c r="D430" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>VARCHAR(512)</t>
         </is>
       </c>
       <c r="E430" s="16" t="inlineStr"/>
       <c r="F430" s="16" t="inlineStr"/>
       <c r="G430" s="16" t="inlineStr">
         <is>
-          <t>是否前五大上游客户（码值：是/否）</t>
+          <t>交易备注（预留：备注含担保/借款/投资关键字贷方发生额筛选用，接口待补充）</t>
         </is>
       </c>
       <c r="H430" s="16" t="inlineStr"/>
       <c r="I430" s="16" t="inlineStr"/>
       <c r="J430" s="8" t="n"/>
-      <c r="K430" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K430" s="8" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="16" t="inlineStr">
@@ -16636,60 +16642,68 @@
       </c>
       <c r="C431" s="16" t="inlineStr">
         <is>
-          <t>remark</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D431" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(512)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E431" s="16" t="inlineStr"/>
-      <c r="F431" s="16" t="inlineStr"/>
+      <c r="F431" s="16" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G431" s="16" t="inlineStr">
         <is>
-          <t>交易备注（预留：备注含担保/借款/投资关键字贷方发生额筛选用，接口待补充）</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H431" s="16" t="inlineStr"/>
-      <c r="I431" s="16" t="inlineStr"/>
+      <c r="I431" s="16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J431" s="8" t="n"/>
       <c r="K431" s="8" t="n"/>
     </row>
     <row r="432">
-      <c r="A432" s="16" t="inlineStr">
-        <is>
-          <t>app_settle_counterparty_info</t>
-        </is>
-      </c>
-      <c r="B432" s="16" t="inlineStr">
-        <is>
-          <t>结算交易对手表</t>
-        </is>
-      </c>
-      <c r="C432" s="16" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D432" s="16" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E432" s="16" t="inlineStr"/>
-      <c r="F432" s="16" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G432" s="16" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H432" s="16" t="inlineStr"/>
-      <c r="I432" s="16" t="inlineStr">
+      <c r="A432" s="27" t="inlineStr">
+        <is>
+          <t>app_payroll_stat_info</t>
+        </is>
+      </c>
+      <c r="B432" s="27" t="inlineStr">
+        <is>
+          <t>代发统计表（月粒度）</t>
+        </is>
+      </c>
+      <c r="C432" s="27" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D432" s="27" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E432" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F432" s="27" t="inlineStr"/>
+      <c r="G432" s="27" t="inlineStr"/>
+      <c r="H432" s="27" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I432" s="27" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -16698,44 +16712,52 @@
       <c r="K432" s="8" t="n"/>
     </row>
     <row r="433">
-      <c r="A433" s="27" t="inlineStr">
+      <c r="A433" s="22" t="inlineStr">
         <is>
           <t>app_payroll_stat_info</t>
         </is>
       </c>
-      <c r="B433" s="27" t="inlineStr">
+      <c r="B433" s="22" t="inlineStr">
         <is>
           <t>代发统计表（月粒度）</t>
         </is>
       </c>
-      <c r="C433" s="27" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D433" s="27" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E433" s="27" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F433" s="27" t="inlineStr"/>
-      <c r="G433" s="27" t="inlineStr"/>
-      <c r="H433" s="27" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I433" s="27" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J433" s="8" t="n"/>
+      <c r="C433" s="22" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D433" s="22" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E433" s="22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F433" s="22" t="inlineStr"/>
+      <c r="G433" s="22" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H433" s="22" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I433" s="22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J433" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K433" s="8" t="n"/>
     </row>
     <row r="434">
@@ -16751,7 +16773,7 @@
       </c>
       <c r="C434" s="22" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D434" s="22" t="inlineStr">
@@ -16759,15 +16781,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E434" s="22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E434" s="22" t="inlineStr"/>
       <c r="F434" s="22" t="inlineStr"/>
       <c r="G434" s="22" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H434" s="22" t="inlineStr">
@@ -16800,36 +16818,28 @@
       </c>
       <c r="C435" s="22" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D435" s="22" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E435" s="22" t="inlineStr"/>
       <c r="F435" s="22" t="inlineStr"/>
       <c r="G435" s="22" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H435" s="22" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H435" s="22" t="inlineStr"/>
       <c r="I435" s="22" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J435" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J435" s="8" t="n"/>
       <c r="K435" s="8" t="n"/>
     </row>
     <row r="436">
@@ -16845,28 +16855,28 @@
       </c>
       <c r="C436" s="22" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>statMonth</t>
         </is>
       </c>
       <c r="D436" s="22" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E436" s="22" t="inlineStr"/>
       <c r="F436" s="22" t="inlineStr"/>
       <c r="G436" s="22" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>统计月份</t>
         </is>
       </c>
       <c r="H436" s="22" t="inlineStr"/>
-      <c r="I436" s="22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J436" s="8" t="n"/>
+      <c r="I436" s="22" t="inlineStr"/>
+      <c r="J436" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K436" s="8" t="n"/>
     </row>
     <row r="437">
@@ -16882,28 +16892,24 @@
       </c>
       <c r="C437" s="22" t="inlineStr">
         <is>
-          <t>statMonth</t>
+          <t>payrollCount</t>
         </is>
       </c>
       <c r="D437" s="22" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="E437" s="22" t="inlineStr"/>
       <c r="F437" s="22" t="inlineStr"/>
       <c r="G437" s="22" t="inlineStr">
         <is>
-          <t>统计月份</t>
+          <t>代发人数</t>
         </is>
       </c>
       <c r="H437" s="22" t="inlineStr"/>
       <c r="I437" s="22" t="inlineStr"/>
-      <c r="J437" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J437" s="8" t="n"/>
       <c r="K437" s="8" t="n"/>
     </row>
     <row r="438">
@@ -16919,19 +16925,19 @@
       </c>
       <c r="C438" s="22" t="inlineStr">
         <is>
-          <t>payrollCount</t>
+          <t>payrollAmount</t>
         </is>
       </c>
       <c r="D438" s="22" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="E438" s="22" t="inlineStr"/>
       <c r="F438" s="22" t="inlineStr"/>
       <c r="G438" s="22" t="inlineStr">
         <is>
-          <t>代发人数</t>
+          <t>代发金额（万元）</t>
         </is>
       </c>
       <c r="H438" s="22" t="inlineStr"/>
@@ -16952,7 +16958,7 @@
       </c>
       <c r="C439" s="22" t="inlineStr">
         <is>
-          <t>payrollAmount</t>
+          <t>countMom</t>
         </is>
       </c>
       <c r="D439" s="22" t="inlineStr">
@@ -16964,7 +16970,7 @@
       <c r="F439" s="22" t="inlineStr"/>
       <c r="G439" s="22" t="inlineStr">
         <is>
-          <t>代发金额（万元）</t>
+          <t>代发人数环比</t>
         </is>
       </c>
       <c r="H439" s="22" t="inlineStr"/>
@@ -16985,7 +16991,7 @@
       </c>
       <c r="C440" s="22" t="inlineStr">
         <is>
-          <t>countMom</t>
+          <t>amountMom</t>
         </is>
       </c>
       <c r="D440" s="22" t="inlineStr">
@@ -16997,7 +17003,7 @@
       <c r="F440" s="22" t="inlineStr"/>
       <c r="G440" s="22" t="inlineStr">
         <is>
-          <t>代发人数环比</t>
+          <t>代发金额环比</t>
         </is>
       </c>
       <c r="H440" s="22" t="inlineStr"/>
@@ -17018,7 +17024,7 @@
       </c>
       <c r="C441" s="22" t="inlineStr">
         <is>
-          <t>amountMom</t>
+          <t>countYoy</t>
         </is>
       </c>
       <c r="D441" s="22" t="inlineStr">
@@ -17030,7 +17036,7 @@
       <c r="F441" s="22" t="inlineStr"/>
       <c r="G441" s="22" t="inlineStr">
         <is>
-          <t>代发金额环比</t>
+          <t>代发人数同比</t>
         </is>
       </c>
       <c r="H441" s="22" t="inlineStr"/>
@@ -17051,7 +17057,7 @@
       </c>
       <c r="C442" s="22" t="inlineStr">
         <is>
-          <t>countYoy</t>
+          <t>amountYoy</t>
         </is>
       </c>
       <c r="D442" s="22" t="inlineStr">
@@ -17063,7 +17069,7 @@
       <c r="F442" s="22" t="inlineStr"/>
       <c r="G442" s="22" t="inlineStr">
         <is>
-          <t>代发人数同比</t>
+          <t>代发金额同比</t>
         </is>
       </c>
       <c r="H442" s="22" t="inlineStr"/>
@@ -17084,60 +17090,68 @@
       </c>
       <c r="C443" s="22" t="inlineStr">
         <is>
-          <t>amountYoy</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D443" s="22" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E443" s="22" t="inlineStr"/>
-      <c r="F443" s="22" t="inlineStr"/>
+      <c r="F443" s="22" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G443" s="22" t="inlineStr">
         <is>
-          <t>代发金额同比</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H443" s="22" t="inlineStr"/>
-      <c r="I443" s="22" t="inlineStr"/>
+      <c r="I443" s="22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J443" s="8" t="n"/>
       <c r="K443" s="8" t="n"/>
     </row>
     <row r="444">
-      <c r="A444" s="22" t="inlineStr">
-        <is>
-          <t>app_payroll_stat_info</t>
-        </is>
-      </c>
-      <c r="B444" s="22" t="inlineStr">
-        <is>
-          <t>代发统计表（月粒度）</t>
-        </is>
-      </c>
-      <c r="C444" s="22" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D444" s="22" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E444" s="22" t="inlineStr"/>
-      <c r="F444" s="22" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G444" s="22" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H444" s="22" t="inlineStr"/>
-      <c r="I444" s="22" t="inlineStr">
+      <c r="A444" s="4" t="inlineStr">
+        <is>
+          <t>app_check_record_info</t>
+        </is>
+      </c>
+      <c r="B444" s="4" t="inlineStr">
+        <is>
+          <t>现场检查打卡记录表</t>
+        </is>
+      </c>
+      <c r="C444" s="4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D444" s="4" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E444" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F444" s="4" t="inlineStr"/>
+      <c r="G444" s="4" t="inlineStr"/>
+      <c r="H444" s="4" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I444" s="4" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -17146,44 +17160,52 @@
       <c r="K444" s="8" t="n"/>
     </row>
     <row r="445">
-      <c r="A445" s="4" t="inlineStr">
+      <c r="A445" s="6" t="inlineStr">
         <is>
           <t>app_check_record_info</t>
         </is>
       </c>
-      <c r="B445" s="4" t="inlineStr">
+      <c r="B445" s="6" t="inlineStr">
         <is>
           <t>现场检查打卡记录表</t>
         </is>
       </c>
-      <c r="C445" s="4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D445" s="4" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E445" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F445" s="4" t="inlineStr"/>
-      <c r="G445" s="4" t="inlineStr"/>
-      <c r="H445" s="4" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I445" s="4" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J445" s="8" t="n"/>
+      <c r="C445" s="6" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D445" s="6" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E445" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F445" s="6" t="inlineStr"/>
+      <c r="G445" s="6" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H445" s="6" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I445" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J445" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K445" s="8" t="n"/>
     </row>
     <row r="446" ht="28" customHeight="1" s="25">
@@ -17199,7 +17221,7 @@
       </c>
       <c r="C446" s="6" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D446" s="6" t="inlineStr">
@@ -17207,15 +17229,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E446" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E446" s="6" t="inlineStr"/>
       <c r="F446" s="6" t="inlineStr"/>
       <c r="G446" s="6" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H446" s="6" t="inlineStr">
@@ -17248,36 +17266,28 @@
       </c>
       <c r="C447" s="6" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D447" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E447" s="6" t="inlineStr"/>
       <c r="F447" s="6" t="inlineStr"/>
       <c r="G447" s="6" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H447" s="6" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H447" s="6" t="inlineStr"/>
       <c r="I447" s="6" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J447" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J447" s="8" t="n"/>
       <c r="K447" s="8" t="n"/>
     </row>
     <row r="448">
@@ -17293,28 +17303,28 @@
       </c>
       <c r="C448" s="6" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>checkInTime</t>
         </is>
       </c>
       <c r="D448" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E448" s="6" t="inlineStr"/>
       <c r="F448" s="6" t="inlineStr"/>
       <c r="G448" s="6" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>打卡日期</t>
         </is>
       </c>
       <c r="H448" s="6" t="inlineStr"/>
-      <c r="I448" s="6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J448" s="8" t="n"/>
+      <c r="I448" s="6" t="inlineStr"/>
+      <c r="J448" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K448" s="8" t="n"/>
     </row>
     <row r="449">
@@ -17330,19 +17340,19 @@
       </c>
       <c r="C449" s="6" t="inlineStr">
         <is>
-          <t>checkInTime</t>
+          <t>checkInAddress</t>
         </is>
       </c>
       <c r="D449" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>VARCHAR(256)</t>
         </is>
       </c>
       <c r="E449" s="6" t="inlineStr"/>
       <c r="F449" s="6" t="inlineStr"/>
       <c r="G449" s="6" t="inlineStr">
         <is>
-          <t>打卡日期</t>
+          <t>打卡地址</t>
         </is>
       </c>
       <c r="H449" s="6" t="inlineStr"/>
@@ -17367,19 +17377,19 @@
       </c>
       <c r="C450" s="6" t="inlineStr">
         <is>
-          <t>checkInAddress</t>
+          <t>visitObj</t>
         </is>
       </c>
       <c r="D450" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(256)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E450" s="6" t="inlineStr"/>
       <c r="F450" s="6" t="inlineStr"/>
       <c r="G450" s="6" t="inlineStr">
         <is>
-          <t>打卡地址</t>
+          <t>拜访对象</t>
         </is>
       </c>
       <c r="H450" s="6" t="inlineStr"/>
@@ -17404,7 +17414,7 @@
       </c>
       <c r="C451" s="6" t="inlineStr">
         <is>
-          <t>visitObj</t>
+          <t>checkInObj</t>
         </is>
       </c>
       <c r="D451" s="6" t="inlineStr">
@@ -17416,7 +17426,7 @@
       <c r="F451" s="6" t="inlineStr"/>
       <c r="G451" s="6" t="inlineStr">
         <is>
-          <t>拜访对象</t>
+          <t>打卡对象</t>
         </is>
       </c>
       <c r="H451" s="6" t="inlineStr"/>
@@ -17441,64 +17451,68 @@
       </c>
       <c r="C452" s="6" t="inlineStr">
         <is>
-          <t>checkInObj</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D452" s="6" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E452" s="6" t="inlineStr"/>
-      <c r="F452" s="6" t="inlineStr"/>
+      <c r="F452" s="6" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G452" s="6" t="inlineStr">
         <is>
-          <t>打卡对象</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H452" s="6" t="inlineStr"/>
-      <c r="I452" s="6" t="inlineStr"/>
-      <c r="J452" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="I452" s="6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J452" s="8" t="n"/>
       <c r="K452" s="8" t="n"/>
     </row>
     <row r="453">
-      <c r="A453" s="6" t="inlineStr">
-        <is>
-          <t>app_check_record_info</t>
-        </is>
-      </c>
-      <c r="B453" s="6" t="inlineStr">
-        <is>
-          <t>现场检查打卡记录表</t>
-        </is>
-      </c>
-      <c r="C453" s="6" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D453" s="6" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E453" s="6" t="inlineStr"/>
-      <c r="F453" s="6" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G453" s="6" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H453" s="6" t="inlineStr"/>
-      <c r="I453" s="6" t="inlineStr">
+      <c r="A453" s="9" t="inlineStr">
+        <is>
+          <t>app_check_opinion_info</t>
+        </is>
+      </c>
+      <c r="B453" s="9" t="inlineStr">
+        <is>
+          <t>批复后续管理要求表</t>
+        </is>
+      </c>
+      <c r="C453" s="9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D453" s="9" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E453" s="9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F453" s="9" t="inlineStr"/>
+      <c r="G453" s="9" t="inlineStr"/>
+      <c r="H453" s="9" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I453" s="9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -17507,44 +17521,52 @@
       <c r="K453" s="8" t="n"/>
     </row>
     <row r="454">
-      <c r="A454" s="9" t="inlineStr">
+      <c r="A454" s="10" t="inlineStr">
         <is>
           <t>app_check_opinion_info</t>
         </is>
       </c>
-      <c r="B454" s="9" t="inlineStr">
+      <c r="B454" s="10" t="inlineStr">
         <is>
           <t>批复后续管理要求表</t>
         </is>
       </c>
-      <c r="C454" s="9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D454" s="9" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E454" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F454" s="9" t="inlineStr"/>
-      <c r="G454" s="9" t="inlineStr"/>
-      <c r="H454" s="9" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I454" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J454" s="8" t="n"/>
+      <c r="C454" s="10" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D454" s="10" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E454" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F454" s="10" t="inlineStr"/>
+      <c r="G454" s="10" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H454" s="10" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I454" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J454" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K454" s="8" t="n"/>
     </row>
     <row r="455">
@@ -17560,7 +17582,7 @@
       </c>
       <c r="C455" s="10" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D455" s="10" t="inlineStr">
@@ -17568,15 +17590,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E455" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E455" s="10" t="inlineStr"/>
       <c r="F455" s="10" t="inlineStr"/>
       <c r="G455" s="10" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H455" s="10" t="inlineStr">
@@ -17609,36 +17627,28 @@
       </c>
       <c r="C456" s="10" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D456" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E456" s="10" t="inlineStr"/>
       <c r="F456" s="10" t="inlineStr"/>
       <c r="G456" s="10" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H456" s="10" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H456" s="10" t="inlineStr"/>
       <c r="I456" s="10" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J456" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J456" s="8" t="n"/>
       <c r="K456" s="8" t="n"/>
     </row>
     <row r="457">
@@ -17654,28 +17664,28 @@
       </c>
       <c r="C457" s="10" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>conditionDesc</t>
         </is>
       </c>
       <c r="D457" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E457" s="10" t="inlineStr"/>
       <c r="F457" s="10" t="inlineStr"/>
       <c r="G457" s="10" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>批复后续管理要求</t>
         </is>
       </c>
       <c r="H457" s="10" t="inlineStr"/>
-      <c r="I457" s="10" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J457" s="8" t="n"/>
+      <c r="I457" s="10" t="inlineStr"/>
+      <c r="J457" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K457" s="8" t="n"/>
     </row>
     <row r="458">
@@ -17691,29 +17701,29 @@
       </c>
       <c r="C458" s="10" t="inlineStr">
         <is>
-          <t>conditionDesc</t>
+          <t>completeStatus</t>
         </is>
       </c>
       <c r="D458" s="10" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E458" s="10" t="inlineStr"/>
       <c r="F458" s="10" t="inlineStr"/>
       <c r="G458" s="10" t="inlineStr">
         <is>
-          <t>批复后续管理要求</t>
+          <t>完成情况（码值：已完成/未完成/部分完成/持续关注，码值待确认）</t>
         </is>
       </c>
       <c r="H458" s="10" t="inlineStr"/>
       <c r="I458" s="10" t="inlineStr"/>
-      <c r="J458" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K458" s="8" t="n"/>
+      <c r="J458" s="8" t="n"/>
+      <c r="K458" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="10" t="inlineStr">
@@ -17728,29 +17738,25 @@
       </c>
       <c r="C459" s="10" t="inlineStr">
         <is>
-          <t>completeStatus</t>
+          <t>conditionInstruction</t>
         </is>
       </c>
       <c r="D459" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E459" s="10" t="inlineStr"/>
       <c r="F459" s="10" t="inlineStr"/>
       <c r="G459" s="10" t="inlineStr">
         <is>
-          <t>完成情况（码值：已完成/未完成/部分完成/持续关注，码值待确认）</t>
+          <t>情况说明</t>
         </is>
       </c>
       <c r="H459" s="10" t="inlineStr"/>
       <c r="I459" s="10" t="inlineStr"/>
       <c r="J459" s="8" t="n"/>
-      <c r="K459" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K459" s="8" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="10" t="inlineStr">
@@ -17765,19 +17771,19 @@
       </c>
       <c r="C460" s="10" t="inlineStr">
         <is>
-          <t>conditionInstruction</t>
+          <t>realCompleteTime</t>
         </is>
       </c>
       <c r="D460" s="10" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E460" s="10" t="inlineStr"/>
       <c r="F460" s="10" t="inlineStr"/>
       <c r="G460" s="10" t="inlineStr">
         <is>
-          <t>情况说明</t>
+          <t>实际完成日期</t>
         </is>
       </c>
       <c r="H460" s="10" t="inlineStr"/>
@@ -17798,19 +17804,19 @@
       </c>
       <c r="C461" s="10" t="inlineStr">
         <is>
-          <t>realCompleteTime</t>
+          <t>itemCategory</t>
         </is>
       </c>
       <c r="D461" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E461" s="10" t="inlineStr"/>
       <c r="F461" s="10" t="inlineStr"/>
       <c r="G461" s="10" t="inlineStr">
         <is>
-          <t>实际完成日期</t>
+          <t>事项类别</t>
         </is>
       </c>
       <c r="H461" s="10" t="inlineStr"/>
@@ -17831,60 +17837,68 @@
       </c>
       <c r="C462" s="10" t="inlineStr">
         <is>
-          <t>itemCategory</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D462" s="10" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E462" s="10" t="inlineStr"/>
-      <c r="F462" s="10" t="inlineStr"/>
+      <c r="F462" s="10" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G462" s="10" t="inlineStr">
         <is>
-          <t>事项类别</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H462" s="10" t="inlineStr"/>
-      <c r="I462" s="10" t="inlineStr"/>
+      <c r="I462" s="10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J462" s="8" t="n"/>
       <c r="K462" s="8" t="n"/>
     </row>
     <row r="463">
-      <c r="A463" s="10" t="inlineStr">
-        <is>
-          <t>app_check_opinion_info</t>
-        </is>
-      </c>
-      <c r="B463" s="10" t="inlineStr">
-        <is>
-          <t>批复后续管理要求表</t>
-        </is>
-      </c>
-      <c r="C463" s="10" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D463" s="10" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E463" s="10" t="inlineStr"/>
-      <c r="F463" s="10" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G463" s="10" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H463" s="10" t="inlineStr"/>
-      <c r="I463" s="10" t="inlineStr">
+      <c r="A463" s="11" t="inlineStr">
+        <is>
+          <t>app_check_index_info</t>
+        </is>
+      </c>
+      <c r="B463" s="11" t="inlineStr">
+        <is>
+          <t>日常检查综合指标表</t>
+        </is>
+      </c>
+      <c r="C463" s="11" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D463" s="11" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E463" s="11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F463" s="11" t="inlineStr"/>
+      <c r="G463" s="11" t="inlineStr"/>
+      <c r="H463" s="11" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I463" s="11" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -17893,44 +17907,52 @@
       <c r="K463" s="8" t="n"/>
     </row>
     <row r="464">
-      <c r="A464" s="11" t="inlineStr">
+      <c r="A464" s="12" t="inlineStr">
         <is>
           <t>app_check_index_info</t>
         </is>
       </c>
-      <c r="B464" s="11" t="inlineStr">
+      <c r="B464" s="12" t="inlineStr">
         <is>
           <t>日常检查综合指标表</t>
         </is>
       </c>
-      <c r="C464" s="11" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D464" s="11" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E464" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F464" s="11" t="inlineStr"/>
-      <c r="G464" s="11" t="inlineStr"/>
-      <c r="H464" s="11" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I464" s="11" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J464" s="8" t="n"/>
+      <c r="C464" s="12" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D464" s="12" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E464" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F464" s="12" t="inlineStr"/>
+      <c r="G464" s="12" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H464" s="12" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I464" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J464" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K464" s="8" t="n"/>
     </row>
     <row r="465">
@@ -17946,7 +17968,7 @@
       </c>
       <c r="C465" s="12" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D465" s="12" t="inlineStr">
@@ -17954,15 +17976,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E465" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E465" s="12" t="inlineStr"/>
       <c r="F465" s="12" t="inlineStr"/>
       <c r="G465" s="12" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H465" s="12" t="inlineStr">
@@ -17995,36 +18013,28 @@
       </c>
       <c r="C466" s="12" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D466" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E466" s="12" t="inlineStr"/>
       <c r="F466" s="12" t="inlineStr"/>
       <c r="G466" s="12" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H466" s="12" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H466" s="12" t="inlineStr"/>
       <c r="I466" s="12" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J466" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J466" s="8" t="n"/>
       <c r="K466" s="8" t="n"/>
     </row>
     <row r="467">
@@ -18040,29 +18050,33 @@
       </c>
       <c r="C467" s="12" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>chineseId</t>
         </is>
       </c>
       <c r="D467" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E467" s="12" t="inlineStr"/>
       <c r="F467" s="12" t="inlineStr"/>
       <c r="G467" s="12" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>指标编号</t>
         </is>
       </c>
       <c r="H467" s="12" t="inlineStr"/>
-      <c r="I467" s="12" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J467" s="8" t="n"/>
-      <c r="K467" s="8" t="n"/>
+      <c r="I467" s="12" t="inlineStr"/>
+      <c r="J467" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K467" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="12" t="inlineStr">
@@ -18077,28 +18091,24 @@
       </c>
       <c r="C468" s="12" t="inlineStr">
         <is>
-          <t>chineseId</t>
+          <t>chineseName</t>
         </is>
       </c>
       <c r="D468" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E468" s="12" t="inlineStr"/>
       <c r="F468" s="12" t="inlineStr"/>
       <c r="G468" s="12" t="inlineStr">
         <is>
-          <t>指标编号</t>
+          <t>指标名称</t>
         </is>
       </c>
       <c r="H468" s="12" t="inlineStr"/>
       <c r="I468" s="12" t="inlineStr"/>
-      <c r="J468" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J468" s="8" t="n"/>
       <c r="K468" s="8" t="inlineStr">
         <is>
           <t>是</t>
@@ -18118,19 +18128,19 @@
       </c>
       <c r="C469" s="12" t="inlineStr">
         <is>
-          <t>chineseName</t>
+          <t>yesNo</t>
         </is>
       </c>
       <c r="D469" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E469" s="12" t="inlineStr"/>
       <c r="F469" s="12" t="inlineStr"/>
       <c r="G469" s="12" t="inlineStr">
         <is>
-          <t>指标名称</t>
+          <t>检查结论（是/否）</t>
         </is>
       </c>
       <c r="H469" s="12" t="inlineStr"/>
@@ -18155,29 +18165,25 @@
       </c>
       <c r="C470" s="12" t="inlineStr">
         <is>
-          <t>yesNo</t>
+          <t>remark</t>
         </is>
       </c>
       <c r="D470" s="12" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E470" s="12" t="inlineStr"/>
       <c r="F470" s="12" t="inlineStr"/>
       <c r="G470" s="12" t="inlineStr">
         <is>
-          <t>检查结论（是/否）</t>
+          <t>说明</t>
         </is>
       </c>
       <c r="H470" s="12" t="inlineStr"/>
       <c r="I470" s="12" t="inlineStr"/>
       <c r="J470" s="8" t="n"/>
-      <c r="K470" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K470" s="8" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="12" t="inlineStr">
@@ -18192,60 +18198,68 @@
       </c>
       <c r="C471" s="12" t="inlineStr">
         <is>
-          <t>remark</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D471" s="12" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E471" s="12" t="inlineStr"/>
-      <c r="F471" s="12" t="inlineStr"/>
+      <c r="F471" s="12" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G471" s="12" t="inlineStr">
         <is>
-          <t>说明</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H471" s="12" t="inlineStr"/>
-      <c r="I471" s="12" t="inlineStr"/>
+      <c r="I471" s="12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J471" s="8" t="n"/>
       <c r="K471" s="8" t="n"/>
     </row>
     <row r="472">
-      <c r="A472" s="12" t="inlineStr">
-        <is>
-          <t>app_check_index_info</t>
-        </is>
-      </c>
-      <c r="B472" s="12" t="inlineStr">
-        <is>
-          <t>日常检查综合指标表</t>
-        </is>
-      </c>
-      <c r="C472" s="12" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D472" s="12" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E472" s="12" t="inlineStr"/>
-      <c r="F472" s="12" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G472" s="12" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H472" s="12" t="inlineStr"/>
-      <c r="I472" s="12" t="inlineStr">
+      <c r="A472" s="13" t="inlineStr">
+        <is>
+          <t>app_reputation_event_info</t>
+        </is>
+      </c>
+      <c r="B472" s="13" t="inlineStr">
+        <is>
+          <t>舆情事件明细表</t>
+        </is>
+      </c>
+      <c r="C472" s="13" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D472" s="13" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E472" s="13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F472" s="13" t="inlineStr"/>
+      <c r="G472" s="13" t="inlineStr"/>
+      <c r="H472" s="13" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I472" s="13" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -18254,44 +18268,52 @@
       <c r="K472" s="8" t="n"/>
     </row>
     <row r="473">
-      <c r="A473" s="13" t="inlineStr">
+      <c r="A473" s="14" t="inlineStr">
         <is>
           <t>app_reputation_event_info</t>
         </is>
       </c>
-      <c r="B473" s="13" t="inlineStr">
+      <c r="B473" s="14" t="inlineStr">
         <is>
           <t>舆情事件明细表</t>
         </is>
       </c>
-      <c r="C473" s="13" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D473" s="13" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E473" s="13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F473" s="13" t="inlineStr"/>
-      <c r="G473" s="13" t="inlineStr"/>
-      <c r="H473" s="13" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I473" s="13" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J473" s="8" t="n"/>
+      <c r="C473" s="14" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D473" s="14" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E473" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F473" s="14" t="inlineStr"/>
+      <c r="G473" s="14" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H473" s="14" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I473" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J473" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K473" s="8" t="n"/>
     </row>
     <row r="474" ht="28" customHeight="1" s="25">
@@ -18307,7 +18329,7 @@
       </c>
       <c r="C474" s="14" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D474" s="14" t="inlineStr">
@@ -18315,15 +18337,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E474" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E474" s="14" t="inlineStr"/>
       <c r="F474" s="14" t="inlineStr"/>
       <c r="G474" s="14" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H474" s="14" t="inlineStr">
@@ -18356,36 +18374,28 @@
       </c>
       <c r="C475" s="14" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D475" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E475" s="14" t="inlineStr"/>
       <c r="F475" s="14" t="inlineStr"/>
       <c r="G475" s="14" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H475" s="14" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H475" s="14" t="inlineStr"/>
       <c r="I475" s="14" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J475" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J475" s="8" t="n"/>
       <c r="K475" s="8" t="n"/>
     </row>
     <row r="476">
@@ -18401,29 +18411,29 @@
       </c>
       <c r="C476" s="14" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>subjectType</t>
         </is>
       </c>
       <c r="D476" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E476" s="14" t="inlineStr"/>
       <c r="F476" s="14" t="inlineStr"/>
       <c r="G476" s="14" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>主体类型（码值：借款人/股东）</t>
         </is>
       </c>
       <c r="H476" s="14" t="inlineStr"/>
-      <c r="I476" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="I476" s="14" t="inlineStr"/>
       <c r="J476" s="8" t="n"/>
-      <c r="K476" s="8" t="n"/>
+      <c r="K476" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="14" t="inlineStr">
@@ -18438,29 +18448,29 @@
       </c>
       <c r="C477" s="14" t="inlineStr">
         <is>
-          <t>subjectType</t>
+          <t>subjectName</t>
         </is>
       </c>
       <c r="D477" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E477" s="14" t="inlineStr"/>
       <c r="F477" s="14" t="inlineStr"/>
       <c r="G477" s="14" t="inlineStr">
         <is>
-          <t>主体类型（码值：借款人/股东）</t>
+          <t>主体名称（借款人名称/股东名称）</t>
         </is>
       </c>
       <c r="H477" s="14" t="inlineStr"/>
       <c r="I477" s="14" t="inlineStr"/>
-      <c r="J477" s="8" t="n"/>
-      <c r="K477" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J477" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K477" s="8" t="n"/>
     </row>
     <row r="478" ht="28" customHeight="1" s="25">
       <c r="A478" s="14" t="inlineStr">
@@ -18475,19 +18485,19 @@
       </c>
       <c r="C478" s="14" t="inlineStr">
         <is>
-          <t>subjectName</t>
+          <t>eventTime</t>
         </is>
       </c>
       <c r="D478" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E478" s="14" t="inlineStr"/>
       <c r="F478" s="14" t="inlineStr"/>
       <c r="G478" s="14" t="inlineStr">
         <is>
-          <t>主体名称（借款人名称/股东名称）</t>
+          <t>舆情发生时间</t>
         </is>
       </c>
       <c r="H478" s="14" t="inlineStr"/>
@@ -18512,19 +18522,19 @@
       </c>
       <c r="C479" s="14" t="inlineStr">
         <is>
-          <t>eventTime</t>
+          <t>eventType</t>
         </is>
       </c>
       <c r="D479" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E479" s="14" t="inlineStr"/>
       <c r="F479" s="14" t="inlineStr"/>
       <c r="G479" s="14" t="inlineStr">
         <is>
-          <t>舆情发生时间</t>
+          <t>舆情类型（码值：证券市场违规/股票戴帽/退市风险/评级下调/高管无法履职/财务造假/其他，待确认）</t>
         </is>
       </c>
       <c r="H479" s="14" t="inlineStr"/>
@@ -18534,7 +18544,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K479" s="8" t="n"/>
+      <c r="K479" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="14" t="inlineStr">
@@ -18549,33 +18563,25 @@
       </c>
       <c r="C480" s="14" t="inlineStr">
         <is>
-          <t>eventType</t>
+          <t>eventDesc</t>
         </is>
       </c>
       <c r="D480" s="14" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="E480" s="14" t="inlineStr"/>
       <c r="F480" s="14" t="inlineStr"/>
       <c r="G480" s="14" t="inlineStr">
         <is>
-          <t>舆情类型（码值：证券市场违规/股票戴帽/退市风险/评级下调/高管无法履职/财务造假/其他，待确认）</t>
+          <t>舆情事件描述</t>
         </is>
       </c>
       <c r="H480" s="14" t="inlineStr"/>
       <c r="I480" s="14" t="inlineStr"/>
-      <c r="J480" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K480" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J480" s="8" t="n"/>
+      <c r="K480" s="8" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="14" t="inlineStr">
@@ -18590,60 +18596,68 @@
       </c>
       <c r="C481" s="14" t="inlineStr">
         <is>
-          <t>eventDesc</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D481" s="14" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E481" s="14" t="inlineStr"/>
-      <c r="F481" s="14" t="inlineStr"/>
+      <c r="F481" s="14" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G481" s="14" t="inlineStr">
         <is>
-          <t>舆情事件描述</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H481" s="14" t="inlineStr"/>
-      <c r="I481" s="14" t="inlineStr"/>
+      <c r="I481" s="14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J481" s="8" t="n"/>
       <c r="K481" s="8" t="n"/>
     </row>
     <row r="482">
-      <c r="A482" s="14" t="inlineStr">
-        <is>
-          <t>app_reputation_event_info</t>
-        </is>
-      </c>
-      <c r="B482" s="14" t="inlineStr">
-        <is>
-          <t>舆情事件明细表</t>
-        </is>
-      </c>
-      <c r="C482" s="14" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D482" s="14" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E482" s="14" t="inlineStr"/>
-      <c r="F482" s="14" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G482" s="14" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H482" s="14" t="inlineStr"/>
-      <c r="I482" s="14" t="inlineStr">
+      <c r="A482" s="15" t="inlineStr">
+        <is>
+          <t>app_guofa_report_info</t>
+        </is>
+      </c>
+      <c r="B482" s="15" t="inlineStr">
+        <is>
+          <t>国发征信信息表</t>
+        </is>
+      </c>
+      <c r="C482" s="15" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D482" s="15" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E482" s="15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F482" s="15" t="inlineStr"/>
+      <c r="G482" s="15" t="inlineStr"/>
+      <c r="H482" s="15" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I482" s="15" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -18652,44 +18666,52 @@
       <c r="K482" s="8" t="n"/>
     </row>
     <row r="483">
-      <c r="A483" s="15" t="inlineStr">
+      <c r="A483" s="16" t="inlineStr">
         <is>
           <t>app_guofa_report_info</t>
         </is>
       </c>
-      <c r="B483" s="15" t="inlineStr">
+      <c r="B483" s="16" t="inlineStr">
         <is>
           <t>国发征信信息表</t>
         </is>
       </c>
-      <c r="C483" s="15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D483" s="15" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E483" s="15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F483" s="15" t="inlineStr"/>
-      <c r="G483" s="15" t="inlineStr"/>
-      <c r="H483" s="15" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I483" s="15" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J483" s="8" t="n"/>
+      <c r="C483" s="16" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D483" s="16" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E483" s="16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F483" s="16" t="inlineStr"/>
+      <c r="G483" s="16" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H483" s="16" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I483" s="16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J483" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K483" s="8" t="n"/>
     </row>
     <row r="484">
@@ -18705,7 +18727,7 @@
       </c>
       <c r="C484" s="16" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D484" s="16" t="inlineStr">
@@ -18713,15 +18735,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E484" s="16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E484" s="16" t="inlineStr"/>
       <c r="F484" s="16" t="inlineStr"/>
       <c r="G484" s="16" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H484" s="16" t="inlineStr">
@@ -18754,36 +18772,28 @@
       </c>
       <c r="C485" s="16" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D485" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E485" s="16" t="inlineStr"/>
       <c r="F485" s="16" t="inlineStr"/>
       <c r="G485" s="16" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H485" s="16" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H485" s="16" t="inlineStr"/>
       <c r="I485" s="16" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J485" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J485" s="8" t="n"/>
       <c r="K485" s="8" t="n"/>
     </row>
     <row r="486">
@@ -18799,27 +18809,27 @@
       </c>
       <c r="C486" s="16" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>queryTime</t>
         </is>
       </c>
       <c r="D486" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E486" s="16" t="inlineStr"/>
       <c r="F486" s="16" t="inlineStr"/>
       <c r="G486" s="16" t="inlineStr">
         <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="H486" s="16" t="inlineStr"/>
-      <c r="I486" s="16" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>国发征信查询时间</t>
+        </is>
+      </c>
+      <c r="H486" s="16" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I486" s="16" t="inlineStr"/>
       <c r="J486" s="8" t="n"/>
       <c r="K486" s="8" t="n"/>
     </row>
@@ -18836,26 +18846,22 @@
       </c>
       <c r="C487" s="16" t="inlineStr">
         <is>
-          <t>queryTime</t>
+          <t>gfRevenue</t>
         </is>
       </c>
       <c r="D487" s="16" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="E487" s="16" t="inlineStr"/>
       <c r="F487" s="16" t="inlineStr"/>
       <c r="G487" s="16" t="inlineStr">
         <is>
-          <t>国发征信查询时间</t>
-        </is>
-      </c>
-      <c r="H487" s="16" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>国发征信营收（万元，上游直给）</t>
+        </is>
+      </c>
+      <c r="H487" s="16" t="inlineStr"/>
       <c r="I487" s="16" t="inlineStr"/>
       <c r="J487" s="8" t="n"/>
       <c r="K487" s="8" t="n"/>
@@ -18873,7 +18879,7 @@
       </c>
       <c r="C488" s="16" t="inlineStr">
         <is>
-          <t>gfRevenue</t>
+          <t>gfReceivable</t>
         </is>
       </c>
       <c r="D488" s="16" t="inlineStr">
@@ -18885,7 +18891,7 @@
       <c r="F488" s="16" t="inlineStr"/>
       <c r="G488" s="16" t="inlineStr">
         <is>
-          <t>国发征信营收（万元，上游直给）</t>
+          <t>国发征信应收账款（万元，上游直给）</t>
         </is>
       </c>
       <c r="H488" s="16" t="inlineStr"/>
@@ -18906,7 +18912,7 @@
       </c>
       <c r="C489" s="16" t="inlineStr">
         <is>
-          <t>gfReceivable</t>
+          <t>gfPayable</t>
         </is>
       </c>
       <c r="D489" s="16" t="inlineStr">
@@ -18918,7 +18924,7 @@
       <c r="F489" s="16" t="inlineStr"/>
       <c r="G489" s="16" t="inlineStr">
         <is>
-          <t>国发征信应收账款（万元，上游直给）</t>
+          <t>国发征信应付账款（万元，上游直给）</t>
         </is>
       </c>
       <c r="H489" s="16" t="inlineStr"/>
@@ -18939,7 +18945,7 @@
       </c>
       <c r="C490" s="16" t="inlineStr">
         <is>
-          <t>gfPayable</t>
+          <t>gfInventory</t>
         </is>
       </c>
       <c r="D490" s="16" t="inlineStr">
@@ -18951,7 +18957,7 @@
       <c r="F490" s="16" t="inlineStr"/>
       <c r="G490" s="16" t="inlineStr">
         <is>
-          <t>国发征信应付账款（万元，上游直给）</t>
+          <t>国发征信存货（万元，上游直给）</t>
         </is>
       </c>
       <c r="H490" s="16" t="inlineStr"/>
@@ -18972,60 +18978,68 @@
       </c>
       <c r="C491" s="16" t="inlineStr">
         <is>
-          <t>gfInventory</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D491" s="16" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E491" s="16" t="inlineStr"/>
-      <c r="F491" s="16" t="inlineStr"/>
+      <c r="F491" s="16" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G491" s="16" t="inlineStr">
         <is>
-          <t>国发征信存货（万元，上游直给）</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H491" s="16" t="inlineStr"/>
-      <c r="I491" s="16" t="inlineStr"/>
+      <c r="I491" s="16" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J491" s="8" t="n"/>
       <c r="K491" s="8" t="n"/>
     </row>
     <row r="492">
-      <c r="A492" s="16" t="inlineStr">
-        <is>
-          <t>app_guofa_report_info</t>
-        </is>
-      </c>
-      <c r="B492" s="16" t="inlineStr">
-        <is>
-          <t>国发征信信息表</t>
-        </is>
-      </c>
-      <c r="C492" s="16" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D492" s="16" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E492" s="16" t="inlineStr"/>
-      <c r="F492" s="16" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G492" s="16" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H492" s="16" t="inlineStr"/>
-      <c r="I492" s="16" t="inlineStr">
+      <c r="A492" s="27" t="inlineStr">
+        <is>
+          <t>app_loan_plan_info</t>
+        </is>
+      </c>
+      <c r="B492" s="27" t="inlineStr">
+        <is>
+          <t>贷款产品还本付息计划表</t>
+        </is>
+      </c>
+      <c r="C492" s="27" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D492" s="27" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E492" s="27" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F492" s="27" t="inlineStr"/>
+      <c r="G492" s="27" t="inlineStr"/>
+      <c r="H492" s="27" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I492" s="27" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -19034,44 +19048,52 @@
       <c r="K492" s="8" t="n"/>
     </row>
     <row r="493">
-      <c r="A493" s="27" t="inlineStr">
+      <c r="A493" s="22" t="inlineStr">
         <is>
           <t>app_loan_plan_info</t>
         </is>
       </c>
-      <c r="B493" s="27" t="inlineStr">
+      <c r="B493" s="22" t="inlineStr">
         <is>
           <t>贷款产品还本付息计划表</t>
         </is>
       </c>
-      <c r="C493" s="27" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D493" s="27" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="E493" s="27" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F493" s="27" t="inlineStr"/>
-      <c r="G493" s="27" t="inlineStr"/>
-      <c r="H493" s="27" t="inlineStr">
-        <is>
-          <t>PRI</t>
-        </is>
-      </c>
-      <c r="I493" s="27" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J493" s="8" t="n"/>
+      <c r="C493" s="22" t="inlineStr">
+        <is>
+          <t>reportNo</t>
+        </is>
+      </c>
+      <c r="D493" s="22" t="inlineStr">
+        <is>
+          <t>VARCHAR(64)</t>
+        </is>
+      </c>
+      <c r="E493" s="22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F493" s="22" t="inlineStr"/>
+      <c r="G493" s="22" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
+      <c r="H493" s="22" t="inlineStr">
+        <is>
+          <t>IDX</t>
+        </is>
+      </c>
+      <c r="I493" s="22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J493" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="K493" s="8" t="n"/>
     </row>
     <row r="494">
@@ -19087,7 +19109,7 @@
       </c>
       <c r="C494" s="22" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D494" s="22" t="inlineStr">
@@ -19095,15 +19117,11 @@
           <t>VARCHAR(64)</t>
         </is>
       </c>
-      <c r="E494" s="22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="E494" s="22" t="inlineStr"/>
       <c r="F494" s="22" t="inlineStr"/>
       <c r="G494" s="22" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H494" s="22" t="inlineStr">
@@ -19136,36 +19154,28 @@
       </c>
       <c r="C495" s="22" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D495" s="22" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
+          <t>VARCHAR(128)</t>
         </is>
       </c>
       <c r="E495" s="22" t="inlineStr"/>
       <c r="F495" s="22" t="inlineStr"/>
       <c r="G495" s="22" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H495" s="22" t="inlineStr">
-        <is>
-          <t>IDX</t>
-        </is>
-      </c>
+          <t>客户名称</t>
+        </is>
+      </c>
+      <c r="H495" s="22" t="inlineStr"/>
       <c r="I495" s="22" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J495" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J495" s="8" t="n"/>
       <c r="K495" s="8" t="n"/>
     </row>
     <row r="496">
@@ -19181,29 +19191,33 @@
       </c>
       <c r="C496" s="22" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>productType</t>
         </is>
       </c>
       <c r="D496" s="22" t="inlineStr">
         <is>
-          <t>VARCHAR(128)</t>
+          <t>VARCHAR(32)</t>
         </is>
       </c>
       <c r="E496" s="22" t="inlineStr"/>
       <c r="F496" s="22" t="inlineStr"/>
       <c r="G496" s="22" t="inlineStr">
         <is>
-          <t>客户名称</t>
+          <t>产品类型（码值：固贷/房地产开发贷款）</t>
         </is>
       </c>
       <c r="H496" s="22" t="inlineStr"/>
-      <c r="I496" s="22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J496" s="8" t="n"/>
-      <c r="K496" s="8" t="n"/>
+      <c r="I496" s="22" t="inlineStr"/>
+      <c r="J496" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K496" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="22" t="inlineStr">
@@ -19218,7 +19232,7 @@
       </c>
       <c r="C497" s="22" t="inlineStr">
         <is>
-          <t>productType</t>
+          <t>nextPayDate</t>
         </is>
       </c>
       <c r="D497" s="22" t="inlineStr">
@@ -19230,7 +19244,7 @@
       <c r="F497" s="22" t="inlineStr"/>
       <c r="G497" s="22" t="inlineStr">
         <is>
-          <t>产品类型（码值：固贷/房地产开发贷款）</t>
+          <t>下次还款日</t>
         </is>
       </c>
       <c r="H497" s="22" t="inlineStr"/>
@@ -19240,11 +19254,7 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K497" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="K497" s="8" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="22" t="inlineStr">
@@ -19259,28 +19269,24 @@
       </c>
       <c r="C498" s="22" t="inlineStr">
         <is>
-          <t>nextPayDate</t>
+          <t>payPrinciPalamt</t>
         </is>
       </c>
       <c r="D498" s="22" t="inlineStr">
         <is>
-          <t>VARCHAR(32)</t>
+          <t>DECIMAL</t>
         </is>
       </c>
       <c r="E498" s="22" t="inlineStr"/>
       <c r="F498" s="22" t="inlineStr"/>
       <c r="G498" s="22" t="inlineStr">
         <is>
-          <t>下次还款日</t>
+          <t>下次还款本金（万元）</t>
         </is>
       </c>
       <c r="H498" s="22" t="inlineStr"/>
       <c r="I498" s="22" t="inlineStr"/>
-      <c r="J498" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+      <c r="J498" s="8" t="n"/>
       <c r="K498" s="8" t="n"/>
     </row>
     <row r="499">
@@ -19296,7 +19302,7 @@
       </c>
       <c r="C499" s="22" t="inlineStr">
         <is>
-          <t>payPrinciPalamt</t>
+          <t>payInterestamt</t>
         </is>
       </c>
       <c r="D499" s="22" t="inlineStr">
@@ -19308,7 +19314,7 @@
       <c r="F499" s="22" t="inlineStr"/>
       <c r="G499" s="22" t="inlineStr">
         <is>
-          <t>下次还款本金（万元）</t>
+          <t>下次还款利息（万元）</t>
         </is>
       </c>
       <c r="H499" s="22" t="inlineStr"/>
@@ -19329,7 +19335,7 @@
       </c>
       <c r="C500" s="22" t="inlineStr">
         <is>
-          <t>payInterestamt</t>
+          <t>payFineAmt</t>
         </is>
       </c>
       <c r="D500" s="22" t="inlineStr">
@@ -19341,7 +19347,7 @@
       <c r="F500" s="22" t="inlineStr"/>
       <c r="G500" s="22" t="inlineStr">
         <is>
-          <t>下次还款利息（万元）</t>
+          <t>下次还款罚息（万元）</t>
         </is>
       </c>
       <c r="H500" s="22" t="inlineStr"/>
@@ -19362,7 +19368,7 @@
       </c>
       <c r="C501" s="22" t="inlineStr">
         <is>
-          <t>payFineAmt</t>
+          <t>compoundInterest</t>
         </is>
       </c>
       <c r="D501" s="22" t="inlineStr">
@@ -19374,7 +19380,7 @@
       <c r="F501" s="22" t="inlineStr"/>
       <c r="G501" s="22" t="inlineStr">
         <is>
-          <t>下次还款罚息（万元）</t>
+          <t>下次还款复利（万元）</t>
         </is>
       </c>
       <c r="H501" s="22" t="inlineStr"/>
@@ -19395,66 +19401,70 @@
       </c>
       <c r="C502" s="22" t="inlineStr">
         <is>
-          <t>compoundInterest</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D502" s="22" t="inlineStr">
         <is>
-          <t>DECIMAL</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="E502" s="22" t="inlineStr"/>
-      <c r="F502" s="22" t="inlineStr"/>
+      <c r="F502" s="22" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
       <c r="G502" s="22" t="inlineStr">
         <is>
-          <t>下次还款复利（万元）</t>
+          <t>入库时间</t>
         </is>
       </c>
       <c r="H502" s="22" t="inlineStr"/>
-      <c r="I502" s="22" t="inlineStr"/>
+      <c r="I502" s="22" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="J502" s="8" t="n"/>
       <c r="K502" s="8" t="n"/>
     </row>
     <row r="503">
-      <c r="A503" s="22" t="inlineStr">
-        <is>
-          <t>app_loan_plan_info</t>
-        </is>
-      </c>
-      <c r="B503" s="22" t="inlineStr">
-        <is>
-          <t>贷款产品还本付息计划表</t>
-        </is>
-      </c>
-      <c r="C503" s="22" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D503" s="22" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E503" s="22" t="inlineStr"/>
-      <c r="F503" s="22" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G503" s="22" t="inlineStr">
-        <is>
-          <t>入库时间</t>
-        </is>
-      </c>
-      <c r="H503" s="22" t="inlineStr"/>
-      <c r="I503" s="22" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J503" s="8" t="n"/>
-      <c r="K503" s="8" t="n"/>
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>app_specific_loan_operate_check_info</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>特定贷款检查表-经营收入类（经营性物业贷款/厂房通贷款，检查租金经营收入/租户/出租预期/抵押物/监管）</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -19469,12 +19479,12 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>reportNo</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -19482,12 +19492,22 @@
           <t>是</t>
         </is>
       </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>PRI</t>
+          <t>IDX</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -19506,22 +19526,17 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="E505" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -19530,11 +19545,6 @@
         </is>
       </c>
       <c r="I505" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J505" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -19553,22 +19563,17 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>VARCHAR(128),</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H506" t="inlineStr">
-        <is>
-          <t>IDX</t>
+          <t>客户名称</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -19590,20 +19595,25 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>objectName</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>VARCHAR(128),</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="I507" t="inlineStr">
+          <t>对象名称（码值：经营性物业贷款/厂房通贷款）</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -19622,27 +19632,17 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>objectName</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>对象名称（码值：经营性物业贷款/厂房通贷款）</t>
-        </is>
-      </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K508" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>用信余额（万元）</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>businessSum</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>用信余额（万元）</t>
+          <t>授信金额（万元）</t>
         </is>
       </c>
     </row>
@@ -19686,17 +19686,22 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>businessSum</t>
+          <t>contractNo</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>授信金额（万元）</t>
+          <t>业务合同编号</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19713,22 +19718,17 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>contractNo</t>
+          <t>duebillTotalBusinessSum</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>业务合同编号</t>
-        </is>
-      </c>
-      <c r="J511" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>用信金额（万元）</t>
         </is>
       </c>
     </row>
@@ -19745,17 +19745,17 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>duebillTotalBusinessSum</t>
+          <t>expectation</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>用信金额（万元）</t>
+          <t>出租情况是否符合预期（码值：是/否，文本结论）</t>
         </is>
       </c>
     </row>
@@ -19772,7 +19772,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>expectation</t>
+          <t>expectation2</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>出租情况是否符合预期（码值：是/否，文本结论）</t>
+          <t>物业收入是否符合预期（码值：是/否，接口字段名保留）</t>
         </is>
       </c>
     </row>
@@ -19799,17 +19799,22 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>expectation2</t>
+          <t>ifChange</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>VARCHAR(32),</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>物业收入是否符合预期（码值：是/否，接口字段名保留）</t>
+          <t>出租情况或物业使用情况是否较授信时发生变化（码值：是/否）</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19826,7 +19831,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>ifChange</t>
+          <t>ifDown</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -19836,7 +19841,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>出租情况或物业使用情况是否较授信时发生变化（码值：是/否）</t>
+          <t>抵押物价值是否有显著下降（码值：是/否）</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
@@ -19858,22 +19863,17 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>ifDown</t>
+          <t>ifDownExplain</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>VARCHAR(32),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>抵押物价值是否有显著下降（码值：是/否）</t>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>抵押物价值显著下降说明</t>
         </is>
       </c>
     </row>
@@ -19890,17 +19890,22 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>ifDownExplain</t>
+          <t>ifOpenAccount</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>VARCHAR(32),</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>抵押物价值显著下降说明</t>
+          <t>是否开立监管账户（码值：是/否）</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -19917,7 +19922,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>ifOpenAccount</t>
+          <t>ifPledge</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -19927,7 +19932,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>是否开立监管账户（码值：是/否）</t>
+          <t>抵押物是否存在查封或其他抵押的情况（码值：是/否）</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
@@ -19949,22 +19954,17 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>ifPledge</t>
+          <t>ifPledgeExplain</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>VARCHAR(32),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>抵押物是否存在查封或其他抵押的情况（码值：是/否）</t>
-        </is>
-      </c>
-      <c r="K519" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>抵押物查封或其他抵押情况说明</t>
         </is>
       </c>
     </row>
@@ -19981,17 +19981,22 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>ifPledgeExplain</t>
+          <t>ifSign</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>VARCHAR(32),</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>抵押物查封或其他抵押情况说明</t>
+          <t>租金监管协议是否已签署（码值：是/否）</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20008,7 +20013,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>ifSign</t>
+          <t>ifSupervise</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -20018,7 +20023,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>租金监管协议是否已签署（码值：是/否）</t>
+          <t>物业经营收入是否需要监管（码值：是/否）</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
@@ -20040,22 +20045,17 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>ifSupervise</t>
+          <t>income</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>VARCHAR(32),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>物业经营收入是否需要监管（码值：是/否）</t>
-        </is>
-      </c>
-      <c r="K522" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>承贷物业的经营收入（本次检查，万元）</t>
         </is>
       </c>
     </row>
@@ -20072,17 +20072,17 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>incomeCompare</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>承贷物业的经营收入（本次检查，万元）</t>
+          <t>承贷物业的经营收入与业务申报方案相比（结论文本）</t>
         </is>
       </c>
     </row>
@@ -20099,17 +20099,17 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>incomeCompare</t>
+          <t>indexYear</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>INT,</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>承贷物业的经营收入与业务申报方案相比（结论文本）</t>
+          <t>年份（本次检查年度，如2026）</t>
         </is>
       </c>
     </row>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>indexYear</t>
+          <t>indexYearCompare</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>年份（本次检查年度，如2026）</t>
+          <t>比较年份（如2025）</t>
         </is>
       </c>
     </row>
@@ -20153,17 +20153,17 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>indexYearCompare</t>
+          <t>lastIncome</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>INT,</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>比较年份（如2025）</t>
+          <t>经营收入（上年/前次，万元）</t>
         </is>
       </c>
     </row>
@@ -20180,17 +20180,17 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>lastIncome</t>
+          <t>lastIncomeCompare</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>经营收入（上年/前次，万元）</t>
+          <t>经营收入与业务申报方案相比（上年/前次）</t>
         </is>
       </c>
     </row>
@@ -20207,17 +20207,17 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>lastIncomeCompare</t>
+          <t>lastLesseeCount</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>INT,</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>经营收入与业务申报方案相比（上年/前次）</t>
+          <t>租户租数（前次/上年）</t>
         </is>
       </c>
     </row>
@@ -20234,17 +20234,17 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>lastLesseeCount</t>
+          <t>lastLesseeCountCompare</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>INT,</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>租户租数（前次/上年）</t>
+          <t>租户租数与业务申报方案相比（前次/上年）</t>
         </is>
       </c>
     </row>
@@ -20261,17 +20261,17 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>lastLesseeCountCompare</t>
+          <t>lastOperateCDIncomeCondition</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>租户租数与业务申报方案相比（前次/上年）</t>
+          <t>承贷物业的经营收入前次检查情况</t>
         </is>
       </c>
     </row>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>lastOperateCDIncomeCondition</t>
+          <t>lastOperateIncomeCondition</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>承贷物业的经营收入前次检查情况</t>
+          <t>前次物业收入及还款来源分析</t>
         </is>
       </c>
     </row>
@@ -20315,17 +20315,17 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>lastOperateIncomeCondition</t>
+          <t>lesseeCount</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>INT,</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>前次物业收入及还款来源分析</t>
+          <t>租户租数（本次）</t>
         </is>
       </c>
     </row>
@@ -20342,17 +20342,17 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>lesseeCount</t>
+          <t>lesseeCountCompare</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>INT,</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>租户租数（本次）</t>
+          <t>租户租数与业务申报方案相比（本次）</t>
         </is>
       </c>
     </row>
@@ -20369,17 +20369,17 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>lesseeCountCompare</t>
+          <t>nominalBalanceSum</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>租户租数与业务申报方案相比（本次）</t>
+          <t>用信敞口余额（万元）</t>
         </is>
       </c>
     </row>
@@ -20396,17 +20396,17 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>nominalBalanceSum</t>
+          <t>operateCDIncomeCondition</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>用信敞口余额（万元）</t>
+          <t>承贷物业的经营收入本次检查情况</t>
         </is>
       </c>
     </row>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>operateCDIncomeCondition</t>
+          <t>operateIncomeCondition</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -20433,7 +20433,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>承贷物业的经营收入本次检查情况</t>
+          <t>物业收入及还款来源分析（本次）</t>
         </is>
       </c>
     </row>
@@ -20450,17 +20450,17 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>operateIncomeCondition</t>
+          <t>productBelongName</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>VARCHAR(128),</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>物业收入及还款来源分析（本次）</t>
+          <t>产品归属</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>productBelongName</t>
+          <t>productName</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -20487,7 +20487,7 @@
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>产品归属</t>
+          <t>基础产品</t>
         </is>
       </c>
     </row>
@@ -20504,7 +20504,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>productName</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -20514,7 +20514,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>基础产品</t>
+          <t>用途</t>
         </is>
       </c>
     </row>
@@ -20531,17 +20531,17 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>repaySum</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>VARCHAR(128),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>用途</t>
+          <t>已还本金（万元）</t>
         </is>
       </c>
     </row>
@@ -20558,17 +20558,17 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>repaySum</t>
+          <t>signExplain</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>已还本金（万元）</t>
+          <t>租金监管协议签署说明</t>
         </is>
       </c>
     </row>
@@ -20585,7 +20585,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>signExplain</t>
+          <t>superviseExplain</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -20595,7 +20595,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>租金监管协议签署说明</t>
+          <t>开立监管账户说明</t>
         </is>
       </c>
     </row>
@@ -20612,17 +20612,17 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>superviseExplain</t>
+          <t>vouchType</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>VARCHAR(32),</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>开立监管账户说明</t>
+          <t>担保方式</t>
         </is>
       </c>
     </row>
@@ -20639,44 +20639,54 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>vouchType</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>VARCHAR(32),</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>担保方式</t>
+          <t>入库时间</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>app_specific_loan_operate_check_info</t>
+          <t>app_specific_loan_project_check_info</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>特定贷款检查表-经营收入类（经营性物业贷款/厂房通贷款，检查租金经营收入/租户/出租预期/抵押物/监管）</t>
+          <t>特定贷款检查表-项目类（固定资产贷款/房地产开发贷款，检查项目资本金/建设进度/资金开票使用/超投/预售）</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>inputtime</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>入库时间</t>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>PRI</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -20693,12 +20703,12 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>reportNo</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(64)</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -20706,12 +20716,22 @@
           <t>是</t>
         </is>
       </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>报告编号</t>
+        </is>
+      </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>PRI</t>
+          <t>IDX</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -20730,22 +20750,17 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>reportNo</t>
+          <t>customerId</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>VARCHAR(64)</t>
-        </is>
-      </c>
-      <c r="E547" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>报告编号</t>
+          <t>客户编号</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -20754,11 +20769,6 @@
         </is>
       </c>
       <c r="I547" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J547" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -20777,22 +20787,17 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>customerId</t>
+          <t>customerName</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>VARCHAR(128),</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>客户编号</t>
-        </is>
-      </c>
-      <c r="H548" t="inlineStr">
-        <is>
-          <t>IDX</t>
+          <t>客户名称</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -20814,20 +20819,25 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>customerName</t>
+          <t>objectName</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>VARCHAR(128),</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>客户名称</t>
-        </is>
-      </c>
-      <c r="I549" t="inlineStr">
+          <t>对象名称（码值：固定资产/房地产开发贷款）</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
         <is>
           <t>是</t>
         </is>
@@ -20846,27 +20856,17 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>objectName</t>
+          <t>balance</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>对象名称（码值：固定资产/房地产开发贷款）</t>
-        </is>
-      </c>
-      <c r="J550" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="K550" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>用信余额（万元）</t>
         </is>
       </c>
     </row>
@@ -20883,7 +20883,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>businessSum</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>用信余额（万元）</t>
+          <t>授信金额（万元）</t>
         </is>
       </c>
     </row>
@@ -20910,17 +20910,17 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>businessSum</t>
+          <t>capitalCheckCondition</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>授信金额（万元）</t>
+          <t>项目资本金情况本次检查情况</t>
         </is>
       </c>
     </row>
@@ -20937,17 +20937,17 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>capitalCheckCondition</t>
+          <t>capitalFundInvoiced</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>项目资本金情况本次检查情况</t>
+          <t>资本金已开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>capitalFundInvoiced</t>
+          <t>capitalFundUnInvoiced</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -20974,7 +20974,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>资本金已开票金额（万元）</t>
+          <t>资本金未开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>capitalFundUnInvoiced</t>
+          <t>capitalFundUsed</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -21001,7 +21001,7 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>资本金未开票金额（万元）</t>
+          <t>资本金已使用金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21018,17 +21018,22 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>capitalFundUsed</t>
+          <t>contractNo</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>VARCHAR(64),</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>资本金已使用金额（万元）</t>
+          <t>业务合同编号</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21045,22 +21050,17 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>contractNo</t>
+          <t>duebillTotalBusinessSum</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>VARCHAR(64),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>业务合同编号</t>
-        </is>
-      </c>
-      <c r="J557" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>用信金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21077,17 +21077,17 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>duebillTotalBusinessSum</t>
+          <t>explain</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>用信金额（万元）</t>
+          <t>说明（项目情况说明）</t>
         </is>
       </c>
     </row>
@@ -21104,17 +21104,22 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>explain</t>
+          <t>ifBuild</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>VARCHAR(32),</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>说明（项目情况说明）</t>
+          <t>是否建设期（码值：是/否）</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21136,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>ifBuild</t>
+          <t>ifConstructionExpect</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -21141,7 +21146,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>是否建设期（码值：是/否）</t>
+          <t>建设期进度是否符合预期（码值：是/否）</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
@@ -21163,7 +21168,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>ifConstructionExpect</t>
+          <t>ifGetPermission</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -21173,7 +21178,7 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>建设期进度是否符合预期（码值：是/否）</t>
+          <t>是否取得预售证（码值：是/否/不涉及）</t>
         </is>
       </c>
       <c r="K561" t="inlineStr">
@@ -21195,7 +21200,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>ifGetPermission</t>
+          <t>ifMatch</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -21205,7 +21210,7 @@
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>是否取得预售证（码值：是/否/不涉及）</t>
+          <t>资金使用是否与项目进度匹配（码值：是/否）</t>
         </is>
       </c>
       <c r="K562" t="inlineStr">
@@ -21227,7 +21232,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>ifMatch</t>
+          <t>ifOpenAccount</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -21237,7 +21242,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>资金使用是否与项目进度匹配（码值：是/否）</t>
+          <t>是否开立监管账户（码值：是/否）</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -21259,7 +21264,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>ifOpenAccount</t>
+          <t>ifOperate</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -21269,7 +21274,7 @@
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>是否开立监管账户（码值：是/否）</t>
+          <t>是否运营期（码值：是/否）</t>
         </is>
       </c>
       <c r="K564" t="inlineStr">
@@ -21291,7 +21296,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>ifOperate</t>
+          <t>ifOverInvest</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -21301,7 +21306,7 @@
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>是否运营期（码值：是/否）</t>
+          <t>是否存在超投情况（码值：是/否）</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
@@ -21323,7 +21328,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>ifOverInvest</t>
+          <t>ifRunExpect</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -21333,7 +21338,7 @@
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>是否存在超投情况（码值：是/否）</t>
+          <t>运营是否符合预期（码值：是/否/不涉及）</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
@@ -21355,7 +21360,7 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>ifRunExpect</t>
+          <t>ifSign</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -21365,7 +21370,7 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>运营是否符合预期（码值：是/否/不涉及）</t>
+          <t>资金监管协议是否已签署（码值：是/否）</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
@@ -21387,22 +21392,17 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>ifSign</t>
+          <t>lastCapitalCheckCondition</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>VARCHAR(32),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>资金监管协议是否已签署（码值：是/否）</t>
-        </is>
-      </c>
-      <c r="K568" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>项目资本金情况前次检查情况</t>
         </is>
       </c>
     </row>
@@ -21419,7 +21419,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>lastCapitalCheckCondition</t>
+          <t>lastPurchaseCheckCondition</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -21429,7 +21429,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>项目资本金情况前次检查情况</t>
+          <t>建安工程或设备采购支出情况前次检查情况</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>lastPurchaseCheckCondition</t>
+          <t>lastRunCheckCondition</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -21456,7 +21456,7 @@
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>建安工程或设备采购支出情况前次检查情况</t>
+          <t>运营检查前次检查情况</t>
         </is>
       </c>
     </row>
@@ -21473,7 +21473,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>lastRunCheckCondition</t>
+          <t>lastScheduleCheckCondition</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>运营检查前次检查情况</t>
+          <t>项目建设进度前次检查情况</t>
         </is>
       </c>
     </row>
@@ -21500,7 +21500,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>lastScheduleCheckCondition</t>
+          <t>lastSuperviseCheckCondition</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>项目建设进度前次检查情况</t>
+          <t>资金监管情况前次检查情况</t>
         </is>
       </c>
     </row>
@@ -21527,17 +21527,17 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>lastSuperviseCheckCondition</t>
+          <t>loanFundInvoiced</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>资金监管情况前次检查情况</t>
+          <t>贷款资金已开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>loanFundInvoiced</t>
+          <t>loanFundUnInvoiced</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>贷款资金已开票金额（万元）</t>
+          <t>贷款资金未开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21581,7 +21581,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>loanFundUnInvoiced</t>
+          <t>loanFundUsed</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -21591,7 +21591,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>贷款资金未开票金额（万元）</t>
+          <t>贷款资金已使用金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21608,7 +21608,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>loanFundUsed</t>
+          <t>nominalBalanceSum</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>贷款资金已使用金额（万元）</t>
+          <t>用信敞口余额（万元）</t>
         </is>
       </c>
     </row>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>nominalBalanceSum</t>
+          <t>otherFundInvoiced</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>用信敞口余额（万元）</t>
+          <t>其他资金已开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21662,7 +21662,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>otherFundInvoiced</t>
+          <t>otherFundUnInvoiced</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -21672,7 +21672,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>其他资金已开票金额（万元）</t>
+          <t>其他资金未开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>otherFundUnInvoiced</t>
+          <t>otherFundUsed</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -21699,7 +21699,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>其他资金未开票金额（万元）</t>
+          <t>其他资金已使用金额（万元）</t>
         </is>
       </c>
     </row>
@@ -21716,17 +21716,17 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>otherFundUsed</t>
+          <t>overInvest</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>其他资金已使用金额（万元）</t>
+          <t>超投情况说明</t>
         </is>
       </c>
     </row>
@@ -21743,17 +21743,17 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>overInvest</t>
+          <t>productBelongName</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>VARCHAR(128),</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>超投情况说明</t>
+          <t>产品归属</t>
         </is>
       </c>
     </row>
@@ -21770,7 +21770,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>productBelongName</t>
+          <t>productName</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>产品归属</t>
+          <t>基础产品</t>
         </is>
       </c>
     </row>
@@ -21797,17 +21797,17 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>productName</t>
+          <t>projectBeginDate</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>VARCHAR(128),</t>
+          <t>VARCHAR(32),</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>基础产品</t>
+          <t>项目启动年月</t>
         </is>
       </c>
     </row>
@@ -21824,7 +21824,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>projectBeginDate</t>
+          <t>projectFinishDate</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -21834,7 +21834,7 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>项目启动年月</t>
+          <t>（预计）项目完工年月</t>
         </is>
       </c>
     </row>
@@ -21851,17 +21851,17 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>projectFinishDate</t>
+          <t>purchaseCheckCondition</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>VARCHAR(32),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>（预计）项目完工年月</t>
+          <t>建安工程或设备采购支出情况本次检查情况</t>
         </is>
       </c>
     </row>
@@ -21878,17 +21878,17 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>purchaseCheckCondition</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>VARCHAR(128),</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>建安工程或设备采购支出情况本次检查情况</t>
+          <t>用途</t>
         </is>
       </c>
     </row>
@@ -21905,17 +21905,17 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>purpose</t>
+          <t>repaySum</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>VARCHAR(128),</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>用途</t>
+          <t>已还本金（万元）</t>
         </is>
       </c>
     </row>
@@ -21932,17 +21932,17 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>repaySum</t>
+          <t>runCheckCondition</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>TEXT,</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>已还本金（万元）</t>
+          <t>运营检查本次检查情况</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>runCheckCondition</t>
+          <t>scheduleCheckCondition</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -21969,7 +21969,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>运营检查本次检查情况</t>
+          <t>项目建设进度本次检查情况</t>
         </is>
       </c>
     </row>
@@ -21986,7 +21986,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>scheduleCheckCondition</t>
+          <t>superviseCheckCondition</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>项目建设进度本次检查情况</t>
+          <t>资金监管情况本次检查情况</t>
         </is>
       </c>
     </row>
@@ -22013,17 +22013,17 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>superviseCheckCondition</t>
+          <t>totalInvestInvoiced</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>TEXT,</t>
+          <t>DECIMAL(18,2),</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>资金监管情况本次检查情况</t>
+          <t>总投资已开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22040,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>totalInvestInvoiced</t>
+          <t>totalInvestUnInvoiced</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>总投资已开票金额（万元）</t>
+          <t>总投资未开票金额（万元）</t>
         </is>
       </c>
     </row>
@@ -22067,7 +22067,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>totalInvestUnInvoiced</t>
+          <t>totalInvestUsed</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -22077,7 +22077,7 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>总投资未开票金额（万元）</t>
+          <t>总投资已使用金额（万元）</t>
         </is>
       </c>
     </row>
@@ -22094,17 +22094,17 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>totalInvestUsed</t>
+          <t>vouchType</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>DECIMAL(18,2),</t>
+          <t>VARCHAR(32),</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>总投资已使用金额（万元）</t>
+          <t>担保方式</t>
         </is>
       </c>
     </row>
@@ -22121,42 +22121,15 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>vouchType</t>
+          <t>inputtime</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>VARCHAR(32),</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
-        <is>
-          <t>担保方式</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>app_specific_loan_project_check_info</t>
-        </is>
-      </c>
-      <c r="B596" t="inlineStr">
-        <is>
-          <t>特定贷款检查表-项目类（固定资产贷款/房地产开发贷款，检查项目资本金/建设进度/资金开票使用/超投/预售）</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>inputtime</t>
-        </is>
-      </c>
-      <c r="D596" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="G596" t="inlineStr">
         <is>
           <t>入库时间</t>
         </is>
@@ -22805,7 +22778,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
